--- a/mass_now.xlsx
+++ b/mass_now.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9024"/>
   </bookViews>
   <sheets>
     <sheet name="DP_요일별" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="210">
-  <si>
-    <t>'26년 19주차 양시 주간 계획 (2026-05-11~2026-05-16)_V1.0</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="209">
+  <si>
+    <t>'26년 20주차 양시 주간 계획 (2026-05-18~2026-05-23)_V1.0</t>
   </si>
   <si>
     <t>담당 : 이운규 010-6455-0564 (72-1555)</t>
@@ -343,13 +343,20 @@
     <t>입고 Plant</t>
   </si>
   <si>
-    <t>RE</t>
-  </si>
-  <si>
-    <t>DS</t>
-  </si>
-  <si>
-    <t>JF0</t>
+    <t>양산기술</t>
+  </si>
+  <si>
+    <t>이준탁</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>JF0
+Mono-Ply</t>
+  </si>
+  <si>
+    <t>PH46</t>
   </si>
   <si>
     <t>L</t>
@@ -362,12 +369,24 @@
   </si>
   <si>
     <t>HK</t>
+  </si>
+  <si>
+    <t>T00</t>
   </si>
   <si>
     <t>60
 (200)</t>
   </si>
   <si>
+    <t>05/18 월</t>
+  </si>
+  <si>
+    <t>RE/DP H183</t>
+  </si>
+  <si>
+    <t>Transfer Dev.</t>
+  </si>
+  <si>
     <t>P95</t>
   </si>
   <si>
@@ -381,7 +400,10 @@
 (N)</t>
   </si>
   <si>
-    <t>B1008</t>
+    <t>DR75421</t>
+  </si>
+  <si>
+    <t>신제작</t>
   </si>
   <si>
     <t>S24</t>
@@ -390,115 +412,49 @@
     <t>B89</t>
   </si>
   <si>
-    <t>B1005</t>
-  </si>
-  <si>
-    <t>ET10203</t>
+    <t>DN69917</t>
+  </si>
+  <si>
+    <t>FA29476</t>
+  </si>
+  <si>
+    <t>FX27532</t>
+  </si>
+  <si>
+    <t>ET10416</t>
+  </si>
+  <si>
+    <t>FH23557</t>
   </si>
   <si>
     <t>ES20424</t>
   </si>
   <si>
+    <t>FX25954</t>
+  </si>
+  <si>
     <t>ET10121</t>
   </si>
   <si>
-    <t>47M</t>
-  </si>
-  <si>
-    <t>정규용</t>
-  </si>
-  <si>
-    <t>입고</t>
-  </si>
-  <si>
-    <t>대전공장</t>
-  </si>
-  <si>
-    <t>양산기술</t>
-  </si>
-  <si>
-    <t>이준탁</t>
-  </si>
-  <si>
-    <t>DP</t>
-  </si>
-  <si>
-    <t>JF505
-Mono-Ply</t>
-  </si>
-  <si>
-    <t>LH41</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>LF</t>
-  </si>
-  <si>
-    <t>T00</t>
-  </si>
-  <si>
-    <t>05/12 화</t>
-  </si>
-  <si>
-    <t>RE/DP H114</t>
-  </si>
-  <si>
-    <t>Transfer Dev.</t>
-  </si>
-  <si>
-    <t>P50</t>
-  </si>
-  <si>
-    <t>DR75422</t>
-  </si>
-  <si>
-    <t>신제작</t>
-  </si>
-  <si>
-    <t>DN69921</t>
-  </si>
-  <si>
-    <t>FA29528</t>
-  </si>
-  <si>
-    <t>FX27527</t>
-  </si>
-  <si>
-    <t>ET10416</t>
-  </si>
-  <si>
-    <t>FH22844</t>
-  </si>
-  <si>
-    <t>FX25992</t>
-  </si>
-  <si>
-    <t>[정규용] 15334 15335
-(금산공장)</t>
-  </si>
-  <si>
-    <t>BC12BP</t>
-  </si>
-  <si>
-    <t>CE09K09</t>
-  </si>
-  <si>
-    <t>40M</t>
-  </si>
-  <si>
-    <t>GU28631</t>
-  </si>
-  <si>
-    <t>GW44006</t>
-  </si>
-  <si>
-    <t>AB115</t>
-  </si>
-  <si>
-    <t>DN69403 수정
-현용 BIC 1124</t>
+    <t>[정규용] 05388 05389</t>
+  </si>
+  <si>
+    <t>BD40AI</t>
+  </si>
+  <si>
+    <t>CE09X09</t>
+  </si>
+  <si>
+    <t>42M</t>
+  </si>
+  <si>
+    <t>GU28784</t>
+  </si>
+  <si>
+    <t>GW54007</t>
+  </si>
+  <si>
+    <t>AD225</t>
   </si>
   <si>
     <t>Ware
@@ -508,118 +464,59 @@
     <t>신우</t>
   </si>
   <si>
-    <t>대기</t>
-  </si>
-  <si>
-    <t>15334</t>
-  </si>
-  <si>
-    <t>입고(미개조)</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>금산공장</t>
-  </si>
-  <si>
-    <t>이병재</t>
-  </si>
-  <si>
-    <t>김상훈</t>
-  </si>
-  <si>
-    <t>JF505</t>
-  </si>
-  <si>
-    <t>265/70R16T</t>
-  </si>
-  <si>
-    <t>PC05</t>
-  </si>
-  <si>
-    <t>05/14 목</t>
-  </si>
-  <si>
-    <t>RE/DS H134</t>
+    <t>김노연</t>
+  </si>
+  <si>
+    <t>05388</t>
+  </si>
+  <si>
+    <t>정규용</t>
+  </si>
+  <si>
+    <t>입고</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>2025-12-11</t>
+  </si>
+  <si>
+    <t>대전공장</t>
+  </si>
+  <si>
+    <t>RE</t>
+  </si>
+  <si>
+    <t>김도형</t>
+  </si>
+  <si>
+    <t>김영광</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>JF0
+Aramid JLB</t>
+  </si>
+  <si>
+    <t>255/55R20V XL</t>
+  </si>
+  <si>
+    <t>IH01A</t>
+  </si>
+  <si>
+    <t>05/20 수</t>
   </si>
   <si>
     <t>Expand</t>
   </si>
   <si>
-    <t>DR71991</t>
-  </si>
-  <si>
-    <t>DN69609</t>
-  </si>
-  <si>
-    <t>FY24911</t>
-  </si>
-  <si>
-    <t>FR02899</t>
-  </si>
-  <si>
-    <t>FW02181</t>
-  </si>
-  <si>
-    <t>610</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>FH24988</t>
-  </si>
-  <si>
-    <t>FX30296</t>
-  </si>
-  <si>
-    <t>DN56899</t>
-  </si>
-  <si>
-    <t>CQB86</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>BD18AP</t>
-  </si>
-  <si>
-    <t>CE09M13</t>
-  </si>
-  <si>
-    <t>48L</t>
-  </si>
-  <si>
-    <t>GU28569</t>
-  </si>
-  <si>
-    <t>GW66006</t>
-  </si>
-  <si>
-    <t>BB315</t>
-  </si>
-  <si>
-    <t>HPW</t>
-  </si>
-  <si>
-    <t>25DH9</t>
-  </si>
-  <si>
-    <t>정규 SIDEMOLD</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>2025-10-28</t>
-  </si>
-  <si>
-    <t>22X30</t>
-  </si>
-  <si>
-    <t>05/15 금</t>
+    <t>P54</t>
   </si>
   <si>
     <t>U36</t>
@@ -629,100 +526,197 @@
 (C)</t>
   </si>
   <si>
+    <t>DR75132</t>
+  </si>
+  <si>
     <t>B1004</t>
   </si>
   <si>
+    <t>DN69508</t>
+  </si>
+  <si>
+    <t>B1005</t>
+  </si>
+  <si>
+    <t>FY25034</t>
+  </si>
+  <si>
+    <t>FR03052</t>
+  </si>
+  <si>
+    <t>ET20271</t>
+  </si>
+  <si>
+    <t>FS00816</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>FHB0045</t>
+  </si>
+  <si>
     <t>ES10262</t>
   </si>
   <si>
+    <t>FX27899</t>
+  </si>
+  <si>
+    <t>ET10151</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>[정규용] 25GZ8 25GZ9
+(개조중)</t>
+  </si>
+  <si>
+    <t>BG03BV</t>
+  </si>
+  <si>
+    <t>CE09X12</t>
+  </si>
+  <si>
+    <t>51M</t>
+  </si>
+  <si>
+    <t>GU29315</t>
+  </si>
+  <si>
+    <t>GW22189</t>
+  </si>
+  <si>
+    <t>AH245</t>
+  </si>
+  <si>
+    <t>Remodel
+Remodel</t>
+  </si>
+  <si>
     <t>에스텍</t>
   </si>
   <si>
-    <t>175/65R14H</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[정규 SIDEMOLD]
-Tread 22X30 22X31
-Side 25DH9 25DJ1</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <t>25GZ8</t>
+  </si>
+  <si>
+    <t>개조중</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>임서윤</t>
+  </si>
+  <si>
+    <t>김상훈</t>
+  </si>
+  <si>
+    <t>JF0</t>
+  </si>
+  <si>
+    <t>235/55R19V XL</t>
+  </si>
+  <si>
+    <t>W340A</t>
+  </si>
+  <si>
+    <t>RE/DS H185</t>
+  </si>
+  <si>
+    <t>P42</t>
+  </si>
+  <si>
+    <t>DR75374</t>
+  </si>
+  <si>
+    <t>DN69868</t>
+  </si>
+  <si>
+    <t>B1007</t>
+  </si>
+  <si>
+    <t>FY24833</t>
+  </si>
+  <si>
+    <t>FX29832</t>
+  </si>
+  <si>
+    <t>FX27526</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>FHB0033</t>
+  </si>
+  <si>
+    <t>FX27873</t>
   </si>
   <si>
     <t>ET11001</t>
   </si>
   <si>
-    <t>P42</t>
-  </si>
-  <si>
-    <t>W340A</t>
-  </si>
-  <si>
-    <t>25GK7</t>
-  </si>
-  <si>
-    <t>AH245+</t>
-  </si>
-  <si>
-    <t>GW22005</t>
-  </si>
-  <si>
-    <t>GU27040</t>
-  </si>
-  <si>
-    <t>BE44AI</t>
-  </si>
-  <si>
-    <t>FX27882</t>
-  </si>
-  <si>
-    <t>FHB0291</t>
-  </si>
-  <si>
-    <t>FX27726</t>
-  </si>
-  <si>
-    <t>FX30397</t>
-  </si>
-  <si>
-    <t>FY24809</t>
-  </si>
-  <si>
-    <t>DR75375</t>
-  </si>
-  <si>
-    <t>235/60R18H XL</t>
-  </si>
-  <si>
-    <t>RE/DS H171</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>이준탁</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <t>BG35BU</t>
+  </si>
+  <si>
+    <t>CE01L12</t>
   </si>
   <si>
     <t>47M</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[정규용] 25GK7 25GK8
+  </si>
+  <si>
+    <t>GU28445</t>
+  </si>
+  <si>
+    <t>GW21965</t>
+  </si>
+  <si>
+    <t>AT235</t>
+  </si>
+  <si>
+    <t>25GJ6</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>[정규용] 25GJ6 25GJ7
 (개조중, 미반출)</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>신제작</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>DN69927</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>T/D Album Car
+현용 BIC 1204</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>P195/65R15H</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>05/21 목</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>RE/DS H139</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -811,14 +805,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color rgb="FF0000FF"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -843,7 +829,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FFFF6600"/>
+      <color rgb="FF6600CC"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -851,15 +837,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FFFF33CC"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF0033CC"/>
+      <color rgb="FF008000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -871,8 +849,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF33CC"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -909,24 +895,6 @@
         <bgColor rgb="FFDAEEF3"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF99FF"/>
-        <bgColor rgb="FFFF99FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEEF3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -955,7 +923,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -976,10 +944,49 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -988,11 +995,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1003,83 +1016,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1087,12 +1040,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFDAEEF3"/>
-      <color rgb="FF0000FF"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1791,769 +1738,773 @@
     </row>
     <row r="3" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2026040158</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="11">
+        <v>1030901</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J3" s="13">
+        <v>4</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="R3" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="S3" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="T3" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="U3" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="V3" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="W3" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="X3" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y3" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z3" s="18">
+        <v>216</v>
+      </c>
+      <c r="AA3" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB3" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC3" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD3" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE3" s="14">
+        <v>140</v>
+      </c>
+      <c r="AF3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="14">
+        <v>1825</v>
+      </c>
+      <c r="AH3" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="AI3" s="14">
+        <v>390</v>
+      </c>
+      <c r="AJ3" s="14">
+        <v>410</v>
+      </c>
+      <c r="AK3" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="AL3" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM3" s="14">
+        <v>520</v>
+      </c>
+      <c r="AN3" s="14">
+        <v>90</v>
+      </c>
+      <c r="AO3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AQ3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AR3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="AT3" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU3" s="14">
+        <v>180</v>
+      </c>
+      <c r="AV3" s="14">
+        <v>27</v>
+      </c>
+      <c r="AW3" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="AX3" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AY3" s="14">
+        <v>170</v>
+      </c>
+      <c r="AZ3" s="14">
+        <v>27</v>
+      </c>
+      <c r="BA3" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="BB3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="BE3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="BG3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH3" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BI3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="BJ3" s="14"/>
+      <c r="BK3" s="14"/>
+      <c r="BL3" s="14">
+        <v>15</v>
+      </c>
+      <c r="BM3" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="BN3" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="BO3" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="BP3" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BQ3" s="17"/>
+      <c r="BR3" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BS3" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="BT3" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU3" s="19">
+        <v>1204</v>
+      </c>
+      <c r="BV3" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="8">
-        <v>2026042739</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="11">
-        <v>1037703</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="J3" s="12">
-        <v>4</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q3" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="R3" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="S3" s="15" t="s">
+      <c r="BW3" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX3" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="BY3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="BZ3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="CA3" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="CB3" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="T3" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="U3" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="V3" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="X3" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y3" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z3" s="16">
-        <v>228</v>
-      </c>
-      <c r="AA3" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC3" s="42" t="s">
-        <v>209</v>
-      </c>
-      <c r="AD3" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE3" s="13">
-        <v>165</v>
-      </c>
-      <c r="AF3" s="13">
-        <v>742</v>
-      </c>
-      <c r="AG3" s="13">
-        <v>2155</v>
-      </c>
-      <c r="AH3" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI3" s="13">
-        <v>460</v>
-      </c>
-      <c r="AJ3" s="13">
-        <v>425</v>
-      </c>
-      <c r="AK3" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="AL3" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="AM3" s="13">
-        <v>610</v>
-      </c>
-      <c r="AN3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO3" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="AP3" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ3" s="13">
-        <v>490</v>
-      </c>
-      <c r="AR3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS3" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="AT3" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="AU3" s="13">
-        <v>190</v>
-      </c>
-      <c r="AV3" s="13">
-        <v>27</v>
-      </c>
-      <c r="AW3" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="AX3" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="AY3" s="13">
-        <v>180</v>
-      </c>
-      <c r="AZ3" s="13">
-        <v>27</v>
-      </c>
-      <c r="BA3" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="BB3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BC3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BD3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BE3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BG3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BH3" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="BI3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BJ3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BK3" s="13"/>
-      <c r="BL3" s="13">
-        <v>18</v>
-      </c>
-      <c r="BM3" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="BN3" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="BO3" s="16"/>
-      <c r="BP3" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="BQ3" s="15"/>
-      <c r="BR3" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="BS3" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="BT3" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="BU3" s="17">
-        <v>1466</v>
-      </c>
-      <c r="BV3" s="18"/>
-      <c r="BW3" s="15"/>
-      <c r="BX3" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="BY3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="BZ3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="CA3" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="CB3" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="CC3" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="CD3" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="CE3" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="CF3" s="15"/>
-      <c r="CG3" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="CH3" s="15"/>
-      <c r="CI3" s="15"/>
-      <c r="CJ3" s="15"/>
-      <c r="CK3" s="15" t="s">
-        <v>113</v>
+      <c r="CC3" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="CD3" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="CE3" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF3" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="CG3" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="CH3" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI3" s="17"/>
+      <c r="CJ3" s="17"/>
+      <c r="CK3" s="17" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="21">
+        <v>2026042894</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="24">
+        <v>1037718</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="J4" s="26">
+        <v>4</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="N4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="T4" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="U4" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="V4" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="W4" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="X4" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y4" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z4" s="31">
+        <v>244</v>
+      </c>
+      <c r="AA4" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB4" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC4" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD4" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="AE4" s="27">
         <v>150</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="8">
-        <v>2026020743</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="G4" s="11">
-        <v>1038853</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J4" s="12">
-        <v>4</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q4" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="R4" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="S4" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="T4" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="V4" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="W4" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="X4" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y4" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z4" s="16">
-        <v>260</v>
-      </c>
-      <c r="AA4" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB4" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC4" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD4" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AE4" s="13">
-        <v>230</v>
-      </c>
-      <c r="AF4" s="13">
-        <v>988</v>
-      </c>
-      <c r="AG4" s="13">
-        <v>2260</v>
-      </c>
-      <c r="AH4" s="13" t="s">
+      <c r="AF4" s="27">
+        <v>716</v>
+      </c>
+      <c r="AG4" s="27">
+        <v>2175</v>
+      </c>
+      <c r="AH4" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="AI4" s="27">
+        <v>460</v>
+      </c>
+      <c r="AJ4" s="27">
+        <v>425</v>
+      </c>
+      <c r="AK4" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="AL4" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM4" s="27">
+        <v>580</v>
+      </c>
+      <c r="AN4" s="27">
+        <v>90</v>
+      </c>
+      <c r="AO4" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP4" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="AQ4" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="AR4" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="AI4" s="13">
-        <v>580</v>
-      </c>
-      <c r="AJ4" s="13">
-        <v>545</v>
-      </c>
-      <c r="AK4" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="AL4" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="AM4" s="13">
-        <v>750</v>
-      </c>
-      <c r="AN4" s="13">
-        <v>90</v>
-      </c>
-      <c r="AO4" s="13" t="s">
+      <c r="AS4" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="AT4" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="AP4" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="AQ4" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="AR4" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="AS4" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="AT4" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU4" s="13">
-        <v>215</v>
-      </c>
-      <c r="AV4" s="13">
-        <v>24</v>
-      </c>
-      <c r="AW4" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="AX4" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AY4" s="13">
+      <c r="AU4" s="27">
         <v>205</v>
       </c>
-      <c r="AZ4" s="13">
-        <v>24</v>
-      </c>
-      <c r="BA4" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="BB4" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BC4" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BD4" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BE4" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF4" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="BG4" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="BH4" s="13" t="s">
+      <c r="AV4" s="27">
+        <v>27</v>
+      </c>
+      <c r="AW4" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="AX4" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="AY4" s="27">
+        <v>195</v>
+      </c>
+      <c r="AZ4" s="27">
+        <v>27</v>
+      </c>
+      <c r="BA4" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="BB4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BE4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BG4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH4" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="BI4" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="BJ4" s="13"/>
-      <c r="BK4" s="13"/>
-      <c r="BL4" s="13">
-        <v>16</v>
-      </c>
-      <c r="BM4" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="BN4" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="BO4" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="BP4" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="BQ4" s="15"/>
-      <c r="BR4" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="BS4" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="BT4" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="BU4" s="17">
-        <v>1289</v>
-      </c>
-      <c r="BV4" s="18"/>
-      <c r="BW4" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="BX4" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="BY4" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="BZ4" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="CA4" s="15" t="s">
+      <c r="BI4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BJ4" s="27"/>
+      <c r="BK4" s="27"/>
+      <c r="BL4" s="27">
+        <v>19</v>
+      </c>
+      <c r="BM4" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="BN4" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="BO4" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="BP4" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="BQ4" s="30"/>
+      <c r="BR4" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="BS4" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="BT4" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="BU4" s="33">
+        <v>1546</v>
+      </c>
+      <c r="BV4" s="34"/>
+      <c r="BW4" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX4" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="BY4" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ4" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="CA4" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="CB4" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="CC4" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="CD4" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="CB4" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="CC4" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="CD4" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="CE4" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="CF4" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="CG4" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="CH4" s="15"/>
-      <c r="CI4" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="CJ4" s="15"/>
-      <c r="CK4" s="15" t="s">
-        <v>113</v>
+      <c r="CE4" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF4" s="30"/>
+      <c r="CG4" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="CH4" s="30"/>
+      <c r="CI4" s="30"/>
+      <c r="CJ4" s="30"/>
+      <c r="CK4" s="30" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="20">
-        <v>2026041940</v>
+      <c r="A5" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="21">
+        <v>2026041320</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="G5" s="24">
-        <v>1019795</v>
+        <v>1038836</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="J5" s="26">
         <v>4</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L5" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="M5" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="N5" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="O5" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="P5" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q5" s="39" t="s">
-        <v>181</v>
+        <v>97</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="N5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="O5" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q5" s="37" t="s">
+        <v>207</v>
       </c>
       <c r="R5" s="29" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="S5" s="30" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="T5" s="31" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="U5" s="31" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="V5" s="31" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="W5" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="X5" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y5" s="25" t="s">
-        <v>127</v>
+        <v>149</v>
+      </c>
+      <c r="X5" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y5" s="27" t="s">
+        <v>151</v>
       </c>
       <c r="Z5" s="31">
-        <v>178</v>
+        <v>272</v>
       </c>
       <c r="AA5" s="31" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="AB5" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC5" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="AD5" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="AE5" s="28">
-        <v>135</v>
-      </c>
-      <c r="AF5" s="28">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="28">
-        <v>1685</v>
-      </c>
-      <c r="AH5" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="AI5" s="28">
-        <v>350</v>
-      </c>
-      <c r="AJ5" s="28">
-        <v>370</v>
-      </c>
-      <c r="AK5" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL5" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="AM5" s="28">
-        <v>460</v>
-      </c>
-      <c r="AN5" s="28">
+        <v>112</v>
+      </c>
+      <c r="AC5" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD5" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE5" s="27">
+        <v>160</v>
+      </c>
+      <c r="AF5" s="27">
+        <v>760</v>
+      </c>
+      <c r="AG5" s="27">
+        <v>2305</v>
+      </c>
+      <c r="AH5" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI5" s="27">
+        <v>490</v>
+      </c>
+      <c r="AJ5" s="27">
+        <v>455</v>
+      </c>
+      <c r="AK5" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="AL5" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM5" s="27">
+        <v>640</v>
+      </c>
+      <c r="AN5" s="27">
         <v>90</v>
       </c>
-      <c r="AO5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="AP5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS5" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="AT5" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU5" s="28">
-        <v>145</v>
-      </c>
-      <c r="AV5" s="28">
-        <v>24</v>
-      </c>
-      <c r="AW5" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="AX5" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="AY5" s="32">
-        <v>135</v>
-      </c>
-      <c r="AZ5" s="28">
-        <v>24</v>
-      </c>
-      <c r="BA5" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="BB5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="BC5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="BD5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="BE5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="BG5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="BH5" s="28" t="s">
+      <c r="AO5" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="AP5" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="AQ5" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="AR5" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="AS5" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="AT5" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="AU5" s="27">
+        <v>230</v>
+      </c>
+      <c r="AV5" s="27">
+        <v>27</v>
+      </c>
+      <c r="AW5" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="AX5" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="AY5" s="27">
+        <v>220</v>
+      </c>
+      <c r="AZ5" s="27">
+        <v>27</v>
+      </c>
+      <c r="BA5" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="BB5" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="BC5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BE5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BF5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BG5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH5" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="BI5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="BJ5" s="28"/>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28">
-        <v>14</v>
+      <c r="BI5" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="BJ5" s="27"/>
+      <c r="BK5" s="27"/>
+      <c r="BL5" s="27">
+        <v>20</v>
       </c>
       <c r="BM5" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="BN5" s="28" t="s">
-        <v>135</v>
+        <v>166</v>
+      </c>
+      <c r="BN5" s="27" t="s">
+        <v>167</v>
       </c>
       <c r="BO5" s="31" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="BP5" s="31" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="BQ5" s="30"/>
       <c r="BR5" s="33" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BS5" s="33" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="BT5" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="BU5" s="33">
+        <v>1626</v>
+      </c>
+      <c r="BV5" s="34"/>
+      <c r="BW5" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="BX5" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="BY5" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ5" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="BU5" s="33">
-        <v>1124</v>
-      </c>
-      <c r="BV5" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="BW5" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="BX5" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="BY5" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="BZ5" s="30" t="s">
-        <v>115</v>
-      </c>
       <c r="CA5" s="30" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="CB5" s="30" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="CC5" s="30" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="CD5" s="30" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="CE5" s="30" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="CF5" s="30"/>
       <c r="CG5" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="CH5" s="30"/>
+        <v>177</v>
+      </c>
+      <c r="CH5" s="30" t="s">
+        <v>178</v>
+      </c>
       <c r="CI5" s="30"/>
       <c r="CJ5" s="30"/>
       <c r="CK5" s="30" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1181102362204724" right="0.1181102362204724" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="27" orientation="landscape" r:id="rId1"/>

--- a/mass_now.xlsx
+++ b/mass_now.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HANTA\OneDrive - HKNC\2026 PI PJT\시험용 계획 양시 계획\양시 계획\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HANTA\OneDrive - HKNC\임시폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9024"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12264"/>
   </bookViews>
   <sheets>
     <sheet name="DP_요일별" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="209">
-  <si>
-    <t>'26년 20주차 양시 주간 계획 (2026-05-18~2026-05-23)_V1.0</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="138">
+  <si>
+    <t>'26년 21주차 양시 주간 계획 (2026-05-25~2026-05-30)_V1.0</t>
   </si>
   <si>
     <t>담당 : 이운규 010-6455-0564 (72-1555)</t>
@@ -343,20 +343,23 @@
     <t>입고 Plant</t>
   </si>
   <si>
-    <t>양산기술</t>
-  </si>
-  <si>
-    <t>이준탁</t>
-  </si>
-  <si>
-    <t>DP</t>
+    <t>RE</t>
+  </si>
+  <si>
+    <t>김노연</t>
+  </si>
+  <si>
+    <t>DS</t>
   </si>
   <si>
     <t>JF0
-Mono-Ply</t>
-  </si>
-  <si>
-    <t>PH46</t>
+Aramid JLB</t>
+  </si>
+  <si>
+    <t>235/40ZR18Y XL</t>
+  </si>
+  <si>
+    <t>K137</t>
   </si>
   <si>
     <t>L</t>
@@ -378,29 +381,26 @@
 (200)</t>
   </si>
   <si>
-    <t>05/18 월</t>
-  </si>
-  <si>
-    <t>RE/DP H183</t>
+    <t>RE/DS H184</t>
   </si>
   <si>
     <t>Transfer Dev.</t>
   </si>
   <si>
-    <t>P95</t>
-  </si>
-  <si>
-    <t>U33</t>
+    <t>P35</t>
+  </si>
+  <si>
+    <t>U35</t>
   </si>
   <si>
     <t>S25</t>
   </si>
   <si>
     <t>-
-(N)</t>
-  </si>
-  <si>
-    <t>DR75421</t>
+(C)</t>
+  </si>
+  <si>
+    <t>DR75458</t>
   </si>
   <si>
     <t>신제작</t>
@@ -412,311 +412,88 @@
     <t>B89</t>
   </si>
   <si>
-    <t>DN69917</t>
-  </si>
-  <si>
-    <t>FA29476</t>
-  </si>
-  <si>
-    <t>FX27532</t>
-  </si>
-  <si>
-    <t>ET10416</t>
-  </si>
-  <si>
-    <t>FH23557</t>
-  </si>
-  <si>
-    <t>ES20424</t>
-  </si>
-  <si>
-    <t>FX25954</t>
-  </si>
-  <si>
-    <t>ET10121</t>
-  </si>
-  <si>
-    <t>[정규용] 05388 05389</t>
-  </si>
-  <si>
-    <t>BD40AI</t>
-  </si>
-  <si>
-    <t>CE09X09</t>
-  </si>
-  <si>
-    <t>42M</t>
-  </si>
-  <si>
-    <t>GU28784</t>
-  </si>
-  <si>
-    <t>GW54007</t>
-  </si>
-  <si>
-    <t>AD225</t>
-  </si>
-  <si>
-    <t>Ware
-Ware</t>
+    <t>DN70001</t>
+  </si>
+  <si>
+    <t>FY24860</t>
+  </si>
+  <si>
+    <t>FX26700</t>
+  </si>
+  <si>
+    <t>ET10203</t>
+  </si>
+  <si>
+    <t>FHB0116</t>
+  </si>
+  <si>
+    <t>ES20425</t>
+  </si>
+  <si>
+    <t>FX26296</t>
+  </si>
+  <si>
+    <t>ET10151</t>
+  </si>
+  <si>
+    <t>STOS</t>
+  </si>
+  <si>
+    <t>BE48AI</t>
+  </si>
+  <si>
+    <t>GU28549</t>
+  </si>
+  <si>
+    <t>GW21956</t>
+  </si>
+  <si>
+    <t>DT115+</t>
   </si>
   <si>
     <t>신우</t>
   </si>
   <si>
-    <t>김노연</t>
-  </si>
-  <si>
-    <t>05388</t>
+    <t>김상훈</t>
+  </si>
+  <si>
+    <t>이준탁</t>
+  </si>
+  <si>
+    <t>24N31</t>
+  </si>
+  <si>
+    <t>45M</t>
   </si>
   <si>
     <t>정규용</t>
   </si>
   <si>
-    <t>입고</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>대전공장</t>
-  </si>
-  <si>
-    <t>RE</t>
-  </si>
-  <si>
-    <t>김도형</t>
-  </si>
-  <si>
-    <t>김영광</t>
-  </si>
-  <si>
-    <t>DS</t>
-  </si>
-  <si>
-    <t>JF0
-Aramid JLB</t>
-  </si>
-  <si>
-    <t>255/55R20V XL</t>
-  </si>
-  <si>
-    <t>IH01A</t>
-  </si>
-  <si>
-    <t>05/20 수</t>
-  </si>
-  <si>
-    <t>Expand</t>
-  </si>
-  <si>
-    <t>P54</t>
-  </si>
-  <si>
-    <t>U36</t>
-  </si>
-  <si>
-    <t>U35
-(C)</t>
-  </si>
-  <si>
-    <t>DR75132</t>
-  </si>
-  <si>
-    <t>B1004</t>
-  </si>
-  <si>
-    <t>DN69508</t>
-  </si>
-  <si>
-    <t>B1005</t>
-  </si>
-  <si>
-    <t>FY25034</t>
-  </si>
-  <si>
-    <t>FR03052</t>
-  </si>
-  <si>
-    <t>ET20271</t>
-  </si>
-  <si>
-    <t>FS00816</t>
-  </si>
-  <si>
-    <t>520</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>FHB0045</t>
-  </si>
-  <si>
-    <t>ES10262</t>
-  </si>
-  <si>
-    <t>FX27899</t>
-  </si>
-  <si>
-    <t>ET10151</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>[정규용] 25GZ8 25GZ9
-(개조중)</t>
-  </si>
-  <si>
-    <t>BG03BV</t>
-  </si>
-  <si>
-    <t>CE09X12</t>
-  </si>
-  <si>
-    <t>51M</t>
-  </si>
-  <si>
-    <t>GU29315</t>
-  </si>
-  <si>
-    <t>GW22189</t>
-  </si>
-  <si>
-    <t>AH245</t>
-  </si>
-  <si>
-    <t>Remodel
-Remodel</t>
-  </si>
-  <si>
-    <t>에스텍</t>
-  </si>
-  <si>
-    <t>25GZ8</t>
-  </si>
-  <si>
     <t>개조중</t>
   </si>
   <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
-    <t>임서윤</t>
-  </si>
-  <si>
-    <t>김상훈</t>
-  </si>
-  <si>
-    <t>JF0</t>
-  </si>
-  <si>
-    <t>235/55R19V XL</t>
-  </si>
-  <si>
-    <t>W340A</t>
-  </si>
-  <si>
-    <t>RE/DS H185</t>
-  </si>
-  <si>
-    <t>P42</t>
-  </si>
-  <si>
-    <t>DR75374</t>
-  </si>
-  <si>
-    <t>DN69868</t>
-  </si>
-  <si>
-    <t>B1007</t>
-  </si>
-  <si>
-    <t>FY24833</t>
-  </si>
-  <si>
-    <t>FX29832</t>
-  </si>
-  <si>
-    <t>FX27526</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>FHB0033</t>
-  </si>
-  <si>
-    <t>FX27873</t>
-  </si>
-  <si>
-    <t>ET11001</t>
-  </si>
-  <si>
-    <t>BG35BU</t>
-  </si>
-  <si>
-    <t>CE01L12</t>
-  </si>
-  <si>
-    <t>47M</t>
-  </si>
-  <si>
-    <t>GU28445</t>
-  </si>
-  <si>
-    <t>GW21965</t>
-  </si>
-  <si>
-    <t>AT235</t>
-  </si>
-  <si>
-    <t>25GJ6</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>[정규용] 25GJ6 25GJ7
-(개조중, 미반출)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>T/D Album Car
-현용 BIC 1204</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>P195/65R15H</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>05/21 목</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>RE/DS H139</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>금산공장</t>
+  </si>
+  <si>
+    <t>[정규용] 24N31 24N32
+(개조중, 금산공장)</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>05/26 화</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -788,22 +565,6 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color rgb="FF0000FF"/>
       <name val="맑은 고딕"/>
@@ -819,30 +580,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF008000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF6600CC"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF008000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -852,13 +589,13 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FFFF33CC"/>
+      <color rgb="FFFF6600"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -889,12 +626,6 @@
         <bgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEEF3"/>
-        <bgColor rgb="FFDAEEF3"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -923,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -944,79 +675,34 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1025,13 +711,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1336,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CL5"/>
+  <dimension ref="A1:CL3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" outlineLevelCol="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1746,767 +1429,253 @@
       <c r="C3" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>93</v>
       </c>
       <c r="E3" s="8">
-        <v>2026040158</v>
-      </c>
-      <c r="F3" s="10" t="s">
+        <v>2026050464</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="11">
-        <v>1030901</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="I3" s="13" t="s">
+      <c r="G3" s="10">
+        <v>1035154</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="J3" s="13">
+      <c r="I3" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="11">
         <v>4</v>
       </c>
-      <c r="K3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="L3" s="13" t="s">
+      <c r="K3" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="L3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="M3" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="N3" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="O3" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="P3" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="Q3" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="R3" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="T3" s="18" t="s">
+      <c r="T3" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="U3" s="18" t="s">
+      <c r="U3" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="V3" s="18" t="s">
+      <c r="V3" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="W3" s="18" t="s">
+      <c r="W3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="X3" s="14" t="s">
+      <c r="X3" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="Y3" s="12" t="s">
+      <c r="Y3" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="Z3" s="18">
-        <v>216</v>
-      </c>
-      <c r="AA3" s="18" t="s">
+      <c r="Z3" s="15">
+        <v>242</v>
+      </c>
+      <c r="AA3" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="AB3" s="18" t="s">
+      <c r="AB3" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="AC3" s="14" t="s">
+      <c r="AC3" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="AD3" s="12" t="s">
+      <c r="AD3" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="AE3" s="14">
-        <v>140</v>
-      </c>
-      <c r="AF3" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="14">
-        <v>1825</v>
-      </c>
-      <c r="AH3" s="14" t="s">
+      <c r="AE3" s="12">
+        <v>105</v>
+      </c>
+      <c r="AF3" s="12">
+        <v>524</v>
+      </c>
+      <c r="AG3" s="12">
+        <v>1880</v>
+      </c>
+      <c r="AH3" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="AI3" s="14">
-        <v>390</v>
-      </c>
-      <c r="AJ3" s="14">
-        <v>410</v>
-      </c>
-      <c r="AK3" s="14" t="s">
+      <c r="AI3" s="12">
+        <v>360</v>
+      </c>
+      <c r="AJ3" s="12">
+        <v>325</v>
+      </c>
+      <c r="AK3" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="AL3" s="14" t="s">
+      <c r="AL3" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="AM3" s="14">
-        <v>520</v>
-      </c>
-      <c r="AN3" s="14">
-        <v>90</v>
-      </c>
-      <c r="AO3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="AP3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="AQ3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="AR3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="AS3" s="14" t="s">
+      <c r="AM3" s="12">
+        <v>550</v>
+      </c>
+      <c r="AN3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AS3" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="AT3" s="14" t="s">
+      <c r="AT3" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="AU3" s="14">
-        <v>180</v>
-      </c>
-      <c r="AV3" s="14">
-        <v>27</v>
-      </c>
-      <c r="AW3" s="14" t="s">
+      <c r="AU3" s="12">
+        <v>210</v>
+      </c>
+      <c r="AV3" s="12">
+        <v>30</v>
+      </c>
+      <c r="AW3" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="AX3" s="14" t="s">
+      <c r="AX3" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="AY3" s="14">
-        <v>170</v>
-      </c>
-      <c r="AZ3" s="14">
-        <v>27</v>
-      </c>
-      <c r="BA3" s="14" t="s">
+      <c r="AY3" s="12">
+        <v>200</v>
+      </c>
+      <c r="AZ3" s="12">
+        <v>30</v>
+      </c>
+      <c r="BA3" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="BB3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="BF3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="BG3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH3" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="BI3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="BJ3" s="14"/>
-      <c r="BK3" s="14"/>
-      <c r="BL3" s="14">
-        <v>15</v>
-      </c>
-      <c r="BM3" s="14" t="s">
+      <c r="BB3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="BD3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="BF3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="BH3" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="BN3" s="14" t="s">
+      <c r="BI3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="BK3" s="12"/>
+      <c r="BL3" s="12">
+        <v>18</v>
+      </c>
+      <c r="BM3" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN3" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="BO3" s="18" t="s">
+      <c r="BO3" s="15"/>
+      <c r="BP3" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="BQ3" s="14"/>
+      <c r="BR3" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="BP3" s="18" t="s">
+      <c r="BS3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="BQ3" s="17"/>
-      <c r="BR3" s="19" t="s">
+      <c r="BT3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="BS3" s="19" t="s">
+      <c r="BU3" s="18">
+        <v>1462</v>
+      </c>
+      <c r="BV3" s="19"/>
+      <c r="BW3" s="14"/>
+      <c r="BX3" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="BT3" s="19" t="s">
+      <c r="BY3" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="BU3" s="19">
-        <v>1204</v>
-      </c>
-      <c r="BV3" s="36" t="s">
-        <v>205</v>
-      </c>
-      <c r="BW3" s="17" t="s">
+      <c r="BZ3" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="BX3" s="20" t="s">
+      <c r="CA3" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="BY3" s="17" t="s">
+      <c r="CB3" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="BZ3" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="CA3" s="17" t="s">
+      <c r="CC3" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="CB3" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CC3" s="17" t="s">
+      <c r="CD3" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="CD3" s="17" t="s">
+      <c r="CE3" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="CF3" s="14"/>
+      <c r="CG3" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="CE3" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="CF3" s="17" t="s">
+      <c r="CH3" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="CG3" s="17" t="s">
+      <c r="CI3" s="14"/>
+      <c r="CJ3" s="14"/>
+      <c r="CK3" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="CH3" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="CI3" s="17"/>
-      <c r="CJ3" s="17"/>
-      <c r="CK3" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" s="21">
-        <v>2026042894</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="G4" s="24">
-        <v>1037718</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="J4" s="26">
-        <v>4</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="N4" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="O4" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="P4" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q4" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="T4" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="U4" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="V4" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="W4" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="X4" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y4" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z4" s="31">
-        <v>244</v>
-      </c>
-      <c r="AA4" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB4" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC4" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD4" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="AE4" s="27">
-        <v>150</v>
-      </c>
-      <c r="AF4" s="27">
-        <v>716</v>
-      </c>
-      <c r="AG4" s="27">
-        <v>2175</v>
-      </c>
-      <c r="AH4" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="AI4" s="27">
-        <v>460</v>
-      </c>
-      <c r="AJ4" s="27">
-        <v>425</v>
-      </c>
-      <c r="AK4" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="AL4" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="AM4" s="27">
-        <v>580</v>
-      </c>
-      <c r="AN4" s="27">
-        <v>90</v>
-      </c>
-      <c r="AO4" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="AP4" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="AQ4" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="AR4" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="AS4" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="AT4" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="AU4" s="27">
-        <v>205</v>
-      </c>
-      <c r="AV4" s="27">
-        <v>27</v>
-      </c>
-      <c r="AW4" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="AX4" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="AY4" s="27">
-        <v>195</v>
-      </c>
-      <c r="AZ4" s="27">
-        <v>27</v>
-      </c>
-      <c r="BA4" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="BB4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BF4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BG4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH4" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="BI4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BJ4" s="27"/>
-      <c r="BK4" s="27"/>
-      <c r="BL4" s="27">
-        <v>19</v>
-      </c>
-      <c r="BM4" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="BN4" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="BO4" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="BP4" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="BQ4" s="30"/>
-      <c r="BR4" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="BS4" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="BT4" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="BU4" s="33">
-        <v>1546</v>
-      </c>
-      <c r="BV4" s="34"/>
-      <c r="BW4" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="BX4" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="BY4" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BZ4" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="CA4" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="CB4" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="CC4" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="CD4" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="CE4" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="CF4" s="30"/>
-      <c r="CG4" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="CH4" s="30"/>
-      <c r="CI4" s="30"/>
-      <c r="CJ4" s="30"/>
-      <c r="CK4" s="30" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="E5" s="21">
-        <v>2026041320</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="G5" s="24">
-        <v>1038836</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="J5" s="26">
-        <v>4</v>
-      </c>
-      <c r="K5" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="N5" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="O5" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="P5" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q5" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="R5" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="S5" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="T5" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="U5" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="V5" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="W5" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="X5" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y5" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z5" s="31">
-        <v>272</v>
-      </c>
-      <c r="AA5" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB5" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC5" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="AD5" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="AE5" s="27">
-        <v>160</v>
-      </c>
-      <c r="AF5" s="27">
-        <v>760</v>
-      </c>
-      <c r="AG5" s="27">
-        <v>2305</v>
-      </c>
-      <c r="AH5" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="AI5" s="27">
-        <v>490</v>
-      </c>
-      <c r="AJ5" s="27">
-        <v>455</v>
-      </c>
-      <c r="AK5" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="AL5" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="AM5" s="27">
-        <v>640</v>
-      </c>
-      <c r="AN5" s="27">
-        <v>90</v>
-      </c>
-      <c r="AO5" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="AP5" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="AQ5" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="AR5" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="AS5" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="AT5" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="AU5" s="27">
-        <v>230</v>
-      </c>
-      <c r="AV5" s="27">
-        <v>27</v>
-      </c>
-      <c r="AW5" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="AX5" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="AY5" s="27">
-        <v>220</v>
-      </c>
-      <c r="AZ5" s="27">
-        <v>27</v>
-      </c>
-      <c r="BA5" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="BB5" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="BC5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BF5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BG5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH5" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="BI5" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="BJ5" s="27"/>
-      <c r="BK5" s="27"/>
-      <c r="BL5" s="27">
-        <v>20</v>
-      </c>
-      <c r="BM5" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="BN5" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="BO5" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="BP5" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="BQ5" s="30"/>
-      <c r="BR5" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="BS5" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="BT5" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="BU5" s="33">
-        <v>1626</v>
-      </c>
-      <c r="BV5" s="34"/>
-      <c r="BW5" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="BX5" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="BY5" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BZ5" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="CA5" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="CB5" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="CC5" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="CD5" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="CE5" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="CF5" s="30"/>
-      <c r="CG5" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="CH5" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="CI5" s="30"/>
-      <c r="CJ5" s="30"/>
-      <c r="CK5" s="30" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1181102362204724" right="0.1181102362204724" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="27" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="27" orientation="landscape"/>
 </worksheet>
 </file>
--- a/mass_now.xlsx
+++ b/mass_now.xlsx
@@ -1,28 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HANTA\OneDrive - HKNC\임시폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HOME\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018C8E4C-B66E-4E7C-B80D-951D3DF30B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12264"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DP_요일별" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="138">
-  <si>
-    <t>'26년 21주차 양시 주간 계획 (2026-05-25~2026-05-30)_V1.0</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="223">
   <si>
     <t>담당 : 이운규 010-6455-0564 (72-1555)</t>
   </si>
@@ -346,20 +344,22 @@
     <t>RE</t>
   </si>
   <si>
+    <t>강병민</t>
+  </si>
+  <si>
     <t>김노연</t>
   </si>
   <si>
-    <t>DS</t>
-  </si>
-  <si>
-    <t>JF0
-Aramid JLB</t>
-  </si>
-  <si>
-    <t>235/40ZR18Y XL</t>
-  </si>
-  <si>
-    <t>K137</t>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>JF505</t>
+  </si>
+  <si>
+    <t>235/55R20H XL</t>
+  </si>
+  <si>
+    <t>W636A</t>
   </si>
   <si>
     <t>L</t>
@@ -381,13 +381,16 @@
 (200)</t>
   </si>
   <si>
-    <t>RE/DS H184</t>
-  </si>
-  <si>
-    <t>Transfer Dev.</t>
-  </si>
-  <si>
-    <t>P35</t>
+    <t>06/01 월</t>
+  </si>
+  <si>
+    <t>RE/DM H101</t>
+  </si>
+  <si>
+    <t>Expand</t>
+  </si>
+  <si>
+    <t>P94</t>
   </si>
   <si>
     <t>U35</t>
@@ -397,103 +400,366 @@
   </si>
   <si>
     <t>-
+(F)</t>
+  </si>
+  <si>
+    <t>DR75467</t>
+  </si>
+  <si>
+    <t>신제작</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>B89</t>
+  </si>
+  <si>
+    <t>DN70016</t>
+  </si>
+  <si>
+    <t>FY24792</t>
+  </si>
+  <si>
+    <t>FX29832</t>
+  </si>
+  <si>
+    <t>ET10416</t>
+  </si>
+  <si>
+    <t>FX27526</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>FH23590</t>
+  </si>
+  <si>
+    <t>ES10262</t>
+  </si>
+  <si>
+    <t>FX27864</t>
+  </si>
+  <si>
+    <t>ET10121</t>
+  </si>
+  <si>
+    <t>BG35BU</t>
+  </si>
+  <si>
+    <t>CE09K13</t>
+  </si>
+  <si>
+    <t>48L</t>
+  </si>
+  <si>
+    <t>GU29032</t>
+  </si>
+  <si>
+    <t>GW22189</t>
+  </si>
+  <si>
+    <t>AT235</t>
+  </si>
+  <si>
+    <t>Remodel
+Remodel</t>
+  </si>
+  <si>
+    <t>에스텍</t>
+  </si>
+  <si>
+    <t>25JF3</t>
+  </si>
+  <si>
+    <t>정규용</t>
+  </si>
+  <si>
+    <t>개조중</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>대전공장</t>
+  </si>
+  <si>
+    <t>이한빛</t>
+  </si>
+  <si>
+    <t>김영광</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>IK41A</t>
+  </si>
+  <si>
+    <t>P37</t>
+  </si>
+  <si>
+    <t>U36</t>
+  </si>
+  <si>
+    <t>U35
 (C)</t>
   </si>
   <si>
-    <t>DR75458</t>
-  </si>
-  <si>
-    <t>신제작</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>B89</t>
-  </si>
-  <si>
-    <t>DN70001</t>
-  </si>
-  <si>
-    <t>FY24860</t>
-  </si>
-  <si>
-    <t>FX26700</t>
-  </si>
-  <si>
-    <t>ET10203</t>
-  </si>
-  <si>
-    <t>FHB0116</t>
-  </si>
-  <si>
-    <t>ES20425</t>
-  </si>
-  <si>
-    <t>FX26296</t>
-  </si>
-  <si>
-    <t>ET10151</t>
+    <t>ET20271</t>
+  </si>
+  <si>
+    <t>AT225</t>
+  </si>
+  <si>
+    <t>Ware
+Ware</t>
+  </si>
+  <si>
+    <t>대광</t>
+  </si>
+  <si>
+    <t>현지용</t>
+  </si>
+  <si>
+    <t>김상훈</t>
+  </si>
+  <si>
+    <t>JF505
+P2000D/2</t>
+  </si>
+  <si>
+    <t>225/55R17V</t>
+  </si>
+  <si>
+    <t>LH43</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>RE/DS H172</t>
+  </si>
+  <si>
+    <t>P61</t>
+  </si>
+  <si>
+    <t>DR75475</t>
+  </si>
+  <si>
+    <t>DN70018</t>
+  </si>
+  <si>
+    <t>FY24549</t>
+  </si>
+  <si>
+    <t>FX31395</t>
+  </si>
+  <si>
+    <t>ET10135</t>
+  </si>
+  <si>
+    <t>FHB0264</t>
+  </si>
+  <si>
+    <t>ES20424</t>
+  </si>
+  <si>
+    <t>FX26554</t>
+  </si>
+  <si>
+    <t>P2000D/2</t>
+  </si>
+  <si>
+    <t>[정규용] 25FZ6 25FZ7</t>
+  </si>
+  <si>
+    <t>BE43AI</t>
+  </si>
+  <si>
+    <t>CE09K11</t>
+  </si>
+  <si>
+    <t>47M</t>
+  </si>
+  <si>
+    <t>GU28435</t>
+  </si>
+  <si>
+    <t>GW21957</t>
+  </si>
+  <si>
+    <t>HPW</t>
+  </si>
+  <si>
+    <t>25FZ6</t>
+  </si>
+  <si>
+    <t>입고</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>정기중</t>
+  </si>
+  <si>
+    <t>06/03 수</t>
+  </si>
+  <si>
+    <t>Quality Improvement</t>
+  </si>
+  <si>
+    <t>215/60R17V</t>
+  </si>
+  <si>
+    <t>K135A</t>
+  </si>
+  <si>
+    <t>T07</t>
+  </si>
+  <si>
+    <t>DR71865</t>
+  </si>
+  <si>
+    <t>B1004</t>
+  </si>
+  <si>
+    <t>DN70021</t>
+  </si>
+  <si>
+    <t>FY24855</t>
+  </si>
+  <si>
+    <t>FX22861</t>
+  </si>
+  <si>
+    <t>FHB0018</t>
+  </si>
+  <si>
+    <t>FX26277</t>
   </si>
   <si>
     <t>STOS</t>
   </si>
   <si>
-    <t>BE48AI</t>
-  </si>
-  <si>
-    <t>GU28549</t>
-  </si>
-  <si>
-    <t>GW21956</t>
-  </si>
-  <si>
-    <t>DT115+</t>
-  </si>
-  <si>
-    <t>신우</t>
-  </si>
-  <si>
-    <t>김상훈</t>
-  </si>
-  <si>
-    <t>이준탁</t>
-  </si>
-  <si>
-    <t>24N31</t>
-  </si>
-  <si>
-    <t>45M</t>
-  </si>
-  <si>
-    <t>정규용</t>
-  </si>
-  <si>
-    <t>개조중</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>금산공장</t>
-  </si>
-  <si>
-    <t>[정규용] 24N31 24N32
-(개조중, 금산공장)</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>05/26 화</t>
+    <t>BE0145</t>
+  </si>
+  <si>
+    <t>CE01X11</t>
+  </si>
+  <si>
+    <t>GU28955</t>
+  </si>
+  <si>
+    <t>AT230</t>
+  </si>
+  <si>
+    <t>Ware
+Ware
+Ware
+Ware</t>
+  </si>
+  <si>
+    <t>21Q61</t>
+  </si>
+  <si>
+    <t>2025-08-09</t>
+  </si>
+  <si>
+    <t>2025-07-14</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>235/50R20V XL</t>
+  </si>
+  <si>
+    <t>DR75174</t>
+  </si>
+  <si>
+    <t>DN70019</t>
+  </si>
+  <si>
+    <t>FY24517</t>
+  </si>
+  <si>
+    <t>FX23051</t>
+  </si>
+  <si>
+    <t>FX23174</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>FH23228</t>
+  </si>
+  <si>
+    <t>FX27894</t>
+  </si>
+  <si>
+    <t>[정규용] 25HC1 25HC2</t>
+  </si>
+  <si>
+    <t>CA04N14</t>
+  </si>
+  <si>
+    <t>GU29024</t>
+  </si>
+  <si>
+    <t>GW22190</t>
+  </si>
+  <si>
+    <t>25HC1</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>06/05 금</t>
+  </si>
+  <si>
+    <t>김노연</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>[정규용] 21Q61 21Q62 22282 22283</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>[정규용] 25JF3 25JF4</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>RE/DS H138</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>RE/DS H173</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>26년 22주차 양시 주간 계획 (2026-06-01~2026-06-06)_V3.0</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -565,8 +831,16 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color rgb="FF0000FF"/>
+      <sz val="16"/>
+      <color rgb="FF00A000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00A000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -580,22 +854,46 @@
       <charset val="129"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF008000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF6600CC"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF008000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF0033CC"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFF6600"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -626,6 +924,12 @@
         <bgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -654,11 +958,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -675,15 +976,63 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -699,23 +1048,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -723,6 +1075,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+      <color rgb="FFEBF1DE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1018,9 +1376,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CL3"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" outlineLevelCol="1" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:CL6"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1052,630 +1410,1401 @@
     <col min="75" max="75" width="16" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="76" max="76" width="10" customWidth="1" collapsed="1"/>
     <col min="77" max="89" width="16" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="90" max="90" width="8.796875" collapsed="1"/>
+    <col min="90" max="90" width="8.75" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:89" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:89" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2"/>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2"/>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="2"/>
-      <c r="BA1" s="2"/>
-      <c r="BB1" s="2"/>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2"/>
-      <c r="BF1" s="2"/>
-      <c r="BG1" s="2"/>
-      <c r="BH1" s="2"/>
-      <c r="BI1" s="2"/>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="3"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-      <c r="BU1" s="2"/>
-      <c r="BV1" s="2" t="s">
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+    </row>
+    <row r="2" spans="1:89" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="BW1" s="2"/>
-      <c r="BX1" s="2"/>
-      <c r="BY1" s="2"/>
-      <c r="BZ1" s="2"/>
-      <c r="CA1" s="2"/>
-      <c r="CB1" s="2"/>
-      <c r="CC1" s="2"/>
-      <c r="CD1" s="2"/>
-      <c r="CE1" s="2"/>
-      <c r="CF1" s="2"/>
-      <c r="CG1" s="2"/>
-      <c r="CH1" s="2"/>
-      <c r="CI1" s="2"/>
-      <c r="CJ1" s="2"/>
-      <c r="CK1" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AV2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AW2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AX2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AY2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AZ2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="BC2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BD2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="BG2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="BK2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="BL2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="BM2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="BO2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="BP2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="BQ2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="BR2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BS2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="BU2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="BV2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BW2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="BX2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="BY2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="BZ2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="CA2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="CB2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="CC2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="CD2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="CE2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="CF2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="CG2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="CH2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="CI2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="CJ2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="CK2" s="3" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="2" spans="1:89" ht="64.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4" t="s">
+    <row r="3" spans="1:89" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="21">
+        <v>2026051036</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="24">
+        <v>1038543</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="J3" s="26">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="4" t="s">
+      <c r="K3" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="N3" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="O3" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="P3" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q3" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="R3" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="S3" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="T3" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="U3" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="V3" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="W3" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="X3" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y3" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z3" s="30">
+        <v>234</v>
+      </c>
+      <c r="AA3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB3" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC3" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="AD3" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE3" s="27">
+        <v>145</v>
+      </c>
+      <c r="AF3" s="27">
+        <v>674</v>
+      </c>
+      <c r="AG3" s="27">
+        <v>1965</v>
+      </c>
+      <c r="AH3" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="AI3" s="27">
+        <v>430</v>
+      </c>
+      <c r="AJ3" s="27">
+        <v>395</v>
+      </c>
+      <c r="AK3" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL3" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="AM3" s="27">
+        <v>550</v>
+      </c>
+      <c r="AN3" s="27">
+        <v>90</v>
+      </c>
+      <c r="AO3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AS3" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="AT3" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="AU3" s="27">
+        <v>200</v>
+      </c>
+      <c r="AV3" s="27">
+        <v>27</v>
+      </c>
+      <c r="AW3" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="AX3" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="AY3" s="27">
+        <v>190</v>
+      </c>
+      <c r="AZ3" s="27">
+        <v>27</v>
+      </c>
+      <c r="BA3" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BD3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BF3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BH3" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ3" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="BK3" s="27"/>
+      <c r="BL3" s="27">
         <v>17</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="S2" s="4" t="s">
+      <c r="BM3" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="BN3" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="BO3" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="BP3" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="BQ3" s="29"/>
+      <c r="BR3" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="BS3" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="BT3" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="BU3" s="31">
+        <v>1383</v>
+      </c>
+      <c r="BV3" s="32"/>
+      <c r="BW3" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="BX3" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="BY3" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ3" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="CA3" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="CB3" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="CC3" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="CD3" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="CE3" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="CF3" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="CG3" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="CH3" s="29"/>
+      <c r="CI3" s="29"/>
+      <c r="CJ3" s="29"/>
+      <c r="CK3" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:89" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="21">
+        <v>2026051823</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="24">
+        <v>1031749</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="J4" s="26">
+        <v>4</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="N4" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q4" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="S4" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="T4" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="U4" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="V4" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="W4" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="X4" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y4" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z4" s="30">
+        <v>230</v>
+      </c>
+      <c r="AA4" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB4" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC4" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD4" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE4" s="27">
+        <v>145</v>
+      </c>
+      <c r="AF4" s="27">
+        <v>662</v>
+      </c>
+      <c r="AG4" s="27">
+        <v>2010</v>
+      </c>
+      <c r="AH4" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="AI4" s="27">
+        <v>430</v>
+      </c>
+      <c r="AJ4" s="27">
+        <v>395</v>
+      </c>
+      <c r="AK4" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="AL4" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="AM4" s="27">
+        <v>700</v>
+      </c>
+      <c r="AN4" s="27">
+        <v>90</v>
+      </c>
+      <c r="AO4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="AS4" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="AT4" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="AU4" s="27">
+        <v>190</v>
+      </c>
+      <c r="AV4" s="27">
+        <v>27</v>
+      </c>
+      <c r="AW4" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="AX4" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="AY4" s="27">
+        <v>180</v>
+      </c>
+      <c r="AZ4" s="27">
+        <v>27</v>
+      </c>
+      <c r="BA4" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BD4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BF4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BH4" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="BI4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ4" s="27"/>
+      <c r="BK4" s="27"/>
+      <c r="BL4" s="27">
+        <v>17</v>
+      </c>
+      <c r="BM4" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="BN4" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="BO4" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="BP4" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="BQ4" s="29"/>
+      <c r="BR4" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="BS4" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="BT4" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="BU4" s="31">
+        <v>1383</v>
+      </c>
+      <c r="BV4" s="32"/>
+      <c r="BW4" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="BX4" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="BY4" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ4" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="CA4" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="CB4" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="CC4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="CD4" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="CE4" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="CF4" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="CG4" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="CH4" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="CI4" s="29"/>
+      <c r="CJ4" s="29"/>
+      <c r="CK4" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:89" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="21">
+        <v>2026051662</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="24">
+        <v>1038793</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="J5" s="26">
+        <v>4</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="N5" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="O5" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="R5" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="S5" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="T5" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="U5" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="V5" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="W5" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="X5" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y5" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z5" s="30">
+        <v>258</v>
+      </c>
+      <c r="AA5" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB5" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC5" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD5" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE5" s="27">
+        <v>135</v>
+      </c>
+      <c r="AF5" s="27">
+        <v>666</v>
+      </c>
+      <c r="AG5" s="27">
+        <v>2170</v>
+      </c>
+      <c r="AH5" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI5" s="27">
+        <v>440</v>
+      </c>
+      <c r="AJ5" s="27">
+        <v>405</v>
+      </c>
+      <c r="AK5" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="AL5" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="AM5" s="27">
+        <v>560</v>
+      </c>
+      <c r="AN5" s="27">
+        <v>90</v>
+      </c>
+      <c r="AO5" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="AP5" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="AQ5" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="AR5" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="AS5" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="AT5" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="AU5" s="27">
+        <v>220</v>
+      </c>
+      <c r="AV5" s="27">
+        <v>27</v>
+      </c>
+      <c r="AW5" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="AX5" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY5" s="27">
+        <v>210</v>
+      </c>
+      <c r="AZ5" s="27">
+        <v>27</v>
+      </c>
+      <c r="BA5" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BD5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BF5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BH5" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ5" s="27"/>
+      <c r="BK5" s="27"/>
+      <c r="BL5" s="27">
         <v>20</v>
       </c>
-      <c r="T2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="W2" s="5" t="s">
+      <c r="BM5" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="BN5" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="BO5" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="BP5" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS5" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="BT5" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="BU5" s="31">
+        <v>1626</v>
+      </c>
+      <c r="BV5" s="32"/>
+      <c r="BW5" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="BX5" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="BY5" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ5" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="CA5" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="CB5" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="CC5" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="CD5" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="CE5" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="CF5" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="CG5" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="CH5" s="29"/>
+      <c r="CI5" s="29"/>
+      <c r="CJ5" s="29"/>
+      <c r="CK5" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:89" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2026051632</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="11">
+        <v>1039090</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" s="12">
+        <v>4</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q6" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="S6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="T6" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="U6" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="V6" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="W6" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="X6" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y6" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z6" s="16">
+        <v>254</v>
+      </c>
+      <c r="AA6" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB6" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC6" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD6" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE6" s="13">
+        <v>155</v>
+      </c>
+      <c r="AF6" s="13">
+        <v>714</v>
+      </c>
+      <c r="AG6" s="13">
+        <v>2235</v>
+      </c>
+      <c r="AH6" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="AI6" s="13">
+        <v>450</v>
+      </c>
+      <c r="AJ6" s="13">
+        <v>415</v>
+      </c>
+      <c r="AK6" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="AL6" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="AM6" s="13">
+        <v>580</v>
+      </c>
+      <c r="AN6" s="13">
+        <v>90</v>
+      </c>
+      <c r="AO6" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP6" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="AQ6" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR6" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="AS6" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AT6" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AU6" s="13">
+        <v>210</v>
+      </c>
+      <c r="AV6" s="13">
         <v>24</v>
       </c>
-      <c r="X2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AO2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AR2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AS2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AU2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AW2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AX2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AZ2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="BA2" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="BB2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="BC2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="BD2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="BE2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="BF2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="BG2" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="BH2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="BI2" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="BJ2" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="BK2" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="BL2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="BM2" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="BN2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="BO2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="BP2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="BQ2" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="BR2" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="BS2" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BT2" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="BU2" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="BV2" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="BW2" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="BX2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="BY2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="BZ2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="CA2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="CB2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="CC2" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="CD2" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="CE2" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="CF2" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="CG2" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="CH2" s="4" t="s">
+      <c r="AW6" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AX6" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY6" s="13">
+        <v>200</v>
+      </c>
+      <c r="AZ6" s="13">
+        <v>24</v>
+      </c>
+      <c r="BA6" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="BD6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="BF6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="BH6" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="CI2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="CJ2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="CK2" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="BI6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ6" s="13"/>
+      <c r="BK6" s="13"/>
+      <c r="BL6" s="13">
+        <v>20</v>
+      </c>
+      <c r="BM6" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="BN6" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="BO6" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="BP6" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="BQ6" s="15"/>
+      <c r="BR6" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS6" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="BT6" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="BU6" s="18">
+        <v>1626</v>
+      </c>
+      <c r="BV6" s="19"/>
+      <c r="BW6" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="BX6" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="BY6" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ6" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="8">
-        <v>2026050464</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G3" s="10">
-        <v>1035154</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="11">
-        <v>4</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q3" s="21" t="s">
+      <c r="CA6" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="CB6" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="CC6" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="CD6" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="CE6" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="CF6" s="15"/>
+      <c r="CG6" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="CH6" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="R3" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="S3" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="X3" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z3" s="15">
-        <v>242</v>
-      </c>
-      <c r="AA3" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB3" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC3" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD3" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE3" s="12">
-        <v>105</v>
-      </c>
-      <c r="AF3" s="12">
-        <v>524</v>
-      </c>
-      <c r="AG3" s="12">
-        <v>1880</v>
-      </c>
-      <c r="AH3" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI3" s="12">
-        <v>360</v>
-      </c>
-      <c r="AJ3" s="12">
-        <v>325</v>
-      </c>
-      <c r="AK3" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="AL3" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="AM3" s="12">
-        <v>550</v>
-      </c>
-      <c r="AN3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AO3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AP3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AQ3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AR3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AS3" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT3" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="AU3" s="12">
-        <v>210</v>
-      </c>
-      <c r="AV3" s="12">
-        <v>30</v>
-      </c>
-      <c r="AW3" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="AX3" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="AY3" s="12">
-        <v>200</v>
-      </c>
-      <c r="AZ3" s="12">
-        <v>30</v>
-      </c>
-      <c r="BA3" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="BB3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="BC3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="BF3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="BG3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH3" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="BI3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="BJ3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="BK3" s="12"/>
-      <c r="BL3" s="12">
-        <v>18</v>
-      </c>
-      <c r="BM3" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="BN3" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BO3" s="15"/>
-      <c r="BP3" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="BQ3" s="14"/>
-      <c r="BR3" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="BS3" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="BT3" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="BU3" s="18">
-        <v>1462</v>
-      </c>
-      <c r="BV3" s="19"/>
-      <c r="BW3" s="14"/>
-      <c r="BX3" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="BY3" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="BZ3" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="CA3" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="CB3" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="CC3" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="CD3" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="CE3" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="CF3" s="14"/>
-      <c r="CG3" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="CH3" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="CI3" s="14"/>
-      <c r="CJ3" s="14"/>
-      <c r="CK3" s="14" t="s">
-        <v>135</v>
+      <c r="CI6" s="15"/>
+      <c r="CJ6" s="15"/>
+      <c r="CK6" s="15" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1181102362204724" right="0.1181102362204724" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="27" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="27" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/mass_now.xlsx
+++ b/mass_now.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="232">
   <si>
     <t>담당</t>
   </si>
@@ -424,134 +424,25 @@
     <t>이준탁</t>
   </si>
   <si>
-    <t>JF5
-P2000D/2</t>
-  </si>
-  <si>
-    <t>1026312</t>
-  </si>
-  <si>
-    <t>225/50R18V XL</t>
-  </si>
-  <si>
-    <t>W330</t>
-  </si>
-  <si>
-    <t>T17</t>
-  </si>
-  <si>
-    <t>06/09 화</t>
-  </si>
-  <si>
-    <t>RE/DS H184</t>
-  </si>
-  <si>
-    <t>Quality Improvement</t>
-  </si>
-  <si>
-    <t>P84</t>
-  </si>
-  <si>
-    <t>DR75259</t>
-  </si>
-  <si>
     <t>B1003</t>
   </si>
   <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>DN70006</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>626</t>
-  </si>
-  <si>
-    <t>1975.0</t>
-  </si>
-  <si>
     <t>FY24753</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>FD24382</t>
-  </si>
-  <si>
     <t>ET10135</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
-    <t>FHB0040</t>
-  </si>
-  <si>
-    <t>ES20425</t>
-  </si>
-  <si>
     <t>200</t>
   </si>
   <si>
-    <t>FX26552</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
     <t>P2000D/2</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>[정규용] 19E15 19E16</t>
-  </si>
-  <si>
-    <t>BE43AI</t>
-  </si>
-  <si>
-    <t>CE09Z11</t>
-  </si>
-  <si>
     <t>47M</t>
   </si>
   <si>
-    <t>GU28436</t>
-  </si>
-  <si>
-    <t>GW21956</t>
-  </si>
-  <si>
-    <t>1462</t>
-  </si>
-  <si>
-    <t>신우</t>
-  </si>
-  <si>
-    <t>김노연</t>
-  </si>
-  <si>
-    <t>19E15</t>
-  </si>
-  <si>
     <t>입고</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>2025-09-09</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
   </si>
   <si>
     <t>JF505
@@ -792,23 +683,19 @@
   </si>
   <si>
     <t>이한빛</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>정기중</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>장시봉</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>담당 : 이운규 010-6455-0564 (72-1555)</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>BE38AI</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>2026052545</t>
@@ -878,26 +765,26 @@
   </si>
   <si>
     <t>이장한</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>26년 23주차 양시 주간 계획 (2026-06-08~2026-06-13)_V3.0</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>RE/DS H152</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>06/12 금</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>26년 23주차 양시 주간 계획 (2026-06-08~2026-06-13)_V4.0</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -979,14 +866,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF008000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFF6600"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -1094,7 +973,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1157,9 +1036,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1199,7 +1075,7 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1510,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CL6"/>
+  <dimension ref="A1:CL5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" outlineLevelCol="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1547,8 +1423,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:89" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
-        <v>266</v>
+      <c r="A1" s="22" t="s">
+        <v>231</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1623,7 +1499,7 @@
       <c r="BT1" s="1"/>
       <c r="BU1" s="1"/>
       <c r="BV1" s="1" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
@@ -1915,28 +1791,28 @@
         <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>91</v>
       </c>
       <c r="E3" s="7">
-        <v>2026051235</v>
+        <v>2026052206</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="J3" s="12">
         <v>4</v>
@@ -1951,25 +1827,25 @@
         <v>95</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="P3" s="13" t="s">
         <v>98</v>
       </c>
       <c r="Q3" s="20" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="U3" s="16" t="s">
         <v>100</v>
@@ -1981,13 +1857,13 @@
         <v>102</v>
       </c>
       <c r="X3" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y3" s="13" t="s">
-        <v>127</v>
+        <v>131</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="Z3" s="16" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AA3" s="16" t="s">
         <v>104</v>
@@ -1996,37 +1872,37 @@
         <v>105</v>
       </c>
       <c r="AC3" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD3" s="11" t="s">
-        <v>103</v>
+        <v>133</v>
+      </c>
+      <c r="AD3" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="AE3" s="13" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AF3" s="13" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AG3" s="13" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="AH3" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AI3" s="13" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AJ3" s="13" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK3" s="13" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AL3" s="19" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="AM3" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AN3" s="13" t="s">
         <v>106</v>
@@ -2044,31 +1920,31 @@
         <v>95</v>
       </c>
       <c r="AS3" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="AT3" s="13" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="AU3" s="13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AV3" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AW3" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AX3" s="13" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="AY3" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AZ3" s="13" t="s">
         <v>108</v>
       </c>
       <c r="BA3" s="13" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="BB3" s="13" t="s">
         <v>95</v>
@@ -2089,29 +1965,29 @@
         <v>95</v>
       </c>
       <c r="BH3" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BI3" s="13" t="s">
         <v>95</v>
       </c>
       <c r="BJ3" s="13" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="BK3" s="13"/>
       <c r="BL3" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="BM3" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="BN3" s="13" t="s">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="BO3" s="16" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="BP3" s="16" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="BQ3" s="15"/>
       <c r="BR3" s="17" t="s">
@@ -2134,35 +2010,33 @@
         <v>153</v>
       </c>
       <c r="BY3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="BZ3" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="CA3" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="BZ3" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA3" s="15" t="s">
-        <v>155</v>
-      </c>
       <c r="CB3" s="15" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="CC3" s="15" t="s">
         <v>114</v>
       </c>
       <c r="CD3" s="15" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="CE3" s="15" t="s">
         <v>153</v>
       </c>
       <c r="CF3" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="CG3" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="CH3" s="15" t="s">
-        <v>159</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="CH3" s="15"/>
       <c r="CI3" s="15"/>
       <c r="CJ3" s="15"/>
       <c r="CK3" s="15" t="s">
@@ -2171,34 +2045,34 @@
     </row>
     <row r="4" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>91</v>
       </c>
       <c r="E4" s="7">
-        <v>2026052206</v>
+        <v>2026051907</v>
       </c>
       <c r="F4" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>163</v>
-      </c>
       <c r="J4" s="12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>93</v>
@@ -2210,22 +2084,22 @@
         <v>95</v>
       </c>
       <c r="N4" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q4" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="R4" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="O4" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q4" s="21" t="s">
+      <c r="S4" s="15" t="s">
         <v>165</v>
-      </c>
-      <c r="R4" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="S4" s="15" t="s">
-        <v>99</v>
       </c>
       <c r="T4" s="16" t="s">
         <v>166</v>
@@ -2237,16 +2111,16 @@
         <v>101</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="X4" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y4" s="11" t="s">
-        <v>103</v>
+        <v>168</v>
+      </c>
+      <c r="Y4" s="13" t="s">
+        <v>117</v>
       </c>
       <c r="Z4" s="16" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="AA4" s="16" t="s">
         <v>104</v>
@@ -2281,53 +2155,53 @@
       <c r="AK4" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AL4" s="19" t="s">
-        <v>137</v>
+      <c r="AL4" s="13" t="s">
+        <v>178</v>
       </c>
       <c r="AM4" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN4" s="13" t="s">
         <v>106</v>
       </c>
       <c r="AO4" s="13" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="AP4" s="13" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="AQ4" s="13" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="AR4" s="13" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="AS4" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AT4" s="13" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="AU4" s="13" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AV4" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AW4" s="13" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AX4" s="13" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="AY4" s="13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AZ4" s="13" t="s">
         <v>108</v>
       </c>
       <c r="BA4" s="13" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="BB4" s="13" t="s">
         <v>95</v>
@@ -2342,84 +2216,86 @@
         <v>95</v>
       </c>
       <c r="BF4" s="13" t="s">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="BG4" s="13" t="s">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="BH4" s="13" t="s">
         <v>86</v>
       </c>
       <c r="BI4" s="13" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="BJ4" s="13" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="BK4" s="13"/>
       <c r="BL4" s="13" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="BM4" s="13" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="BN4" s="13" t="s">
-        <v>242</v>
+        <v>192</v>
       </c>
       <c r="BO4" s="16" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="BP4" s="16" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="BQ4" s="15"/>
       <c r="BR4" s="17" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="BS4" s="17" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="BT4" s="17" t="s">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="BU4" s="17" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="BV4" s="18"/>
       <c r="BW4" s="15" t="s">
         <v>112</v>
       </c>
       <c r="BX4" s="19" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="BY4" s="15" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="BZ4" s="15" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="CA4" s="15" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="CB4" s="15" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="CC4" s="15" t="s">
         <v>114</v>
       </c>
       <c r="CD4" s="15" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="CE4" s="15" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="CF4" s="15" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="CG4" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="CH4" s="15"/>
+        <v>200</v>
+      </c>
+      <c r="CH4" s="15" t="s">
+        <v>201</v>
+      </c>
       <c r="CI4" s="15"/>
       <c r="CJ4" s="15"/>
       <c r="CK4" s="15" t="s">
@@ -2427,523 +2303,264 @@
       </c>
     </row>
     <row r="5" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="A5" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="7">
-        <v>2026051907</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="J5" s="12">
-        <v>8</v>
-      </c>
-      <c r="K5" s="12" t="s">
+      <c r="E5" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="J5" s="27">
+        <v>4</v>
+      </c>
+      <c r="K5" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="M5" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="N5" s="13" t="s">
+      <c r="M5" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="N5" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="O5" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="P5" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q5" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="R5" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="S5" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="T5" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="U5" s="16" t="s">
+      <c r="O5" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="P5" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q5" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="R5" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="S5" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T5" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="U5" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="V5" s="16" t="s">
+      <c r="V5" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="W5" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="X5" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="Y5" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z5" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA5" s="16" t="s">
+      <c r="W5" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="X5" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y5" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z5" s="30">
+        <v>232</v>
+      </c>
+      <c r="AA5" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AB5" s="16" t="s">
+      <c r="AB5" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AC5" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="AD5" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="AE5" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF5" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="AG5" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH5" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="AI5" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="AJ5" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="AK5" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="AL5" s="13" t="s">
+      <c r="AC5" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="AM5" s="13" t="s">
+      <c r="AD5" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE5" s="28">
+        <v>135</v>
+      </c>
+      <c r="AF5" s="28">
+        <v>628</v>
+      </c>
+      <c r="AG5" s="28">
+        <v>1935</v>
+      </c>
+      <c r="AH5" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI5" s="28">
+        <v>410</v>
+      </c>
+      <c r="AJ5" s="28">
+        <v>375</v>
+      </c>
+      <c r="AK5" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="AN5" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO5" s="13" t="s">
+      <c r="AL5" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="AP5" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="AQ5" s="13" t="s">
+      <c r="AM5" s="28">
+        <v>520</v>
+      </c>
+      <c r="AN5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="AQ5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="AR5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS5" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="AR5" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AS5" s="13" t="s">
+      <c r="AT5" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="AT5" s="13" t="s">
+      <c r="AU5" s="28">
+        <v>190</v>
+      </c>
+      <c r="AV5" s="28">
+        <v>27</v>
+      </c>
+      <c r="AW5" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="AU5" s="13" t="s">
+      <c r="AX5" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="AY5" s="28">
+        <v>180</v>
+      </c>
+      <c r="AZ5" s="28">
+        <v>27</v>
+      </c>
+      <c r="BA5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BB5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BC5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BD5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BE5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BG5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BH5" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BJ5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="BM5" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="AV5" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AW5" s="13" t="s">
+      <c r="BN5" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="AX5" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="AY5" s="13" t="s">
+      <c r="BO5" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="AZ5" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BA5" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="BB5" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="BC5" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="BD5" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="BE5" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF5" s="13" t="s">
+      <c r="BP5" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BQ5" s="29"/>
+      <c r="BR5" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="BS5" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="BT5" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="BG5" s="13" t="s">
+      <c r="BU5" s="31">
+        <v>1383</v>
+      </c>
+      <c r="BV5" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="BH5" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="BI5" s="13" t="s">
+      <c r="BW5" s="29"/>
+      <c r="BX5" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="BJ5" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="BK5" s="13"/>
-      <c r="BL5" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="BM5" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="BN5" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="BO5" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="BP5" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="BQ5" s="15"/>
-      <c r="BR5" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="BS5" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT5" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="BU5" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="BV5" s="18"/>
-      <c r="BW5" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="BX5" s="19" t="s">
-        <v>113</v>
-      </c>
       <c r="BY5" s="15" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="BZ5" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA5" s="15" t="s">
-        <v>234</v>
+        <v>95</v>
+      </c>
+      <c r="CA5" s="15">
+        <v>26634</v>
       </c>
       <c r="CB5" s="15" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="CC5" s="15" t="s">
         <v>114</v>
       </c>
       <c r="CD5" s="15" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="CE5" s="15" t="s">
-        <v>113</v>
+        <v>225</v>
       </c>
       <c r="CF5" s="15" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="CG5" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="CH5" s="15" t="s">
-        <v>237</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="CH5" s="15"/>
       <c r="CI5" s="15"/>
       <c r="CJ5" s="15"/>
       <c r="CK5" s="15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="J6" s="28">
-        <v>4</v>
-      </c>
-      <c r="K6" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="L6" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="N6" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="O6" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="P6" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q6" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="R6" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="S6" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="T6" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="U6" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="V6" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="W6" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="X6" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="Y6" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z6" s="31">
-        <v>232</v>
-      </c>
-      <c r="AA6" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB6" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC6" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="AD6" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE6" s="29">
-        <v>135</v>
-      </c>
-      <c r="AF6" s="29">
-        <v>628</v>
-      </c>
-      <c r="AG6" s="29">
-        <v>1935</v>
-      </c>
-      <c r="AH6" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="AI6" s="29">
-        <v>410</v>
-      </c>
-      <c r="AJ6" s="29">
-        <v>375</v>
-      </c>
-      <c r="AK6" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="AL6" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="AM6" s="29">
-        <v>520</v>
-      </c>
-      <c r="AN6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="AO6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="AQ6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="AS6" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="AT6" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="AU6" s="29">
-        <v>190</v>
-      </c>
-      <c r="AV6" s="29">
-        <v>27</v>
-      </c>
-      <c r="AW6" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="AX6" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="AY6" s="29">
-        <v>180</v>
-      </c>
-      <c r="AZ6" s="29">
-        <v>27</v>
-      </c>
-      <c r="BA6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BB6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BC6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BD6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BE6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BG6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BH6" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="BI6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BJ6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BK6" s="29"/>
-      <c r="BL6" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="BM6" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="BN6" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="BO6" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="BP6" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="BQ6" s="30"/>
-      <c r="BR6" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="BS6" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="BT6" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU6" s="32">
-        <v>1383</v>
-      </c>
-      <c r="BV6" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="BW6" s="30"/>
-      <c r="BX6" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="BY6" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="BZ6" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="CA6" s="15">
-        <v>26634</v>
-      </c>
-      <c r="CB6" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="CC6" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="CD6" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="CE6" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="CF6" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="CG6" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="CH6" s="15"/>
-      <c r="CI6" s="15"/>
-      <c r="CJ6" s="15"/>
-      <c r="CK6" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1181102362204724" right="0.1181102362204724" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="27" orientation="landscape" r:id="rId1"/>

--- a/mass_now.xlsx
+++ b/mass_now.xlsx
@@ -19,7 +19,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="373">
+  <si>
+    <t>담당 : 이운규 010-6455-0564 (72-1555)</t>
+  </si>
   <si>
     <t>담당</t>
   </si>
@@ -52,9 +55,6 @@
   </si>
   <si>
     <t>T/L</t>
-  </si>
-  <si>
-    <t>B/W</t>
   </si>
   <si>
     <t>USE</t>
@@ -340,22 +340,28 @@
     <t>RE</t>
   </si>
   <si>
-    <t>김영광</t>
+    <t>김상훈</t>
   </si>
   <si>
     <t>DS</t>
   </si>
   <si>
-    <t>JF5</t>
+    <t>-</t>
+  </si>
+  <si>
+    <t>1038838</t>
+  </si>
+  <si>
+    <t>245/45R21H XL</t>
+  </si>
+  <si>
+    <t>IH01A</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>HK</t>
@@ -371,420 +377,845 @@
     <t>Expand</t>
   </si>
   <si>
+    <t>P54</t>
+  </si>
+  <si>
     <t>U36</t>
   </si>
   <si>
     <t>S25</t>
+  </si>
+  <si>
+    <t>신제작</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>B89</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>47M</t>
+  </si>
+  <si>
+    <t>Ware
+Ware</t>
+  </si>
+  <si>
+    <t>에스텍</t>
+  </si>
+  <si>
+    <t>25GZ2</t>
+  </si>
+  <si>
+    <t>정규용</t>
+  </si>
+  <si>
+    <t>입고</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>대전공장</t>
+  </si>
+  <si>
+    <t>정기중</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>JF5</t>
+  </si>
+  <si>
+    <t>1031750</t>
+  </si>
+  <si>
+    <t>235/50R19V</t>
+  </si>
+  <si>
+    <t>K135A</t>
+  </si>
+  <si>
+    <t>T03</t>
+  </si>
+  <si>
+    <t>06/16 화</t>
+  </si>
+  <si>
+    <t>RE/DM H102</t>
+  </si>
+  <si>
+    <t>Quality Improvement</t>
+  </si>
+  <si>
+    <t>P37</t>
   </si>
   <si>
     <t>U35
 (C)</t>
   </si>
   <si>
-    <t>신제작</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>B89</t>
+    <t>DR71906</t>
+  </si>
+  <si>
+    <t>B1004</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>DN69309</t>
+  </si>
+  <si>
+    <t>B1007</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>652</t>
+  </si>
+  <si>
+    <t>2090.0</t>
+  </si>
+  <si>
+    <t>FY24517</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>FX22861</t>
+  </si>
+  <si>
+    <t>ET20271</t>
+  </si>
+  <si>
+    <t>700</t>
   </si>
   <si>
     <t>90</t>
   </si>
   <si>
+    <t>FH24572</t>
+  </si>
+  <si>
+    <t>ES20424</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>FX29002</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>ET10121</t>
+  </si>
+  <si>
+    <t>STOS</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>[정규용] 22304 22305</t>
+  </si>
+  <si>
+    <t>BG48AP</t>
+  </si>
+  <si>
+    <t>CE09P11</t>
+  </si>
+  <si>
+    <t>GU28155</t>
+  </si>
+  <si>
+    <t>GW22186</t>
+  </si>
+  <si>
+    <t>AT225</t>
+  </si>
+  <si>
+    <t>1542</t>
+  </si>
+  <si>
+    <t>혜원</t>
+  </si>
+  <si>
+    <t>22304</t>
+  </si>
+  <si>
+    <t>2025-09-06</t>
+  </si>
+  <si>
+    <t>2025-09-05</t>
+  </si>
+  <si>
+    <t>이한빛</t>
+  </si>
+  <si>
+    <t>김영광</t>
+  </si>
+  <si>
+    <t>1038795</t>
+  </si>
+  <si>
+    <t>265/45R20V XL</t>
+  </si>
+  <si>
+    <t>IK41A</t>
+  </si>
+  <si>
+    <t>06/17 수</t>
+  </si>
+  <si>
+    <t>RE/DS H138</t>
+  </si>
+  <si>
+    <t>DR75474</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>DN70030</t>
+  </si>
+  <si>
+    <t>680</t>
+  </si>
+  <si>
+    <t>2180.0</t>
+  </si>
+  <si>
+    <t>FY24833</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>FX23722</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t>FD23345</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
+    <t>FHB0085</t>
+  </si>
+  <si>
     <t>ES10262</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>ET10121</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>AT225</t>
-  </si>
-  <si>
-    <t>Ware
-Ware</t>
+    <t>240</t>
+  </si>
+  <si>
+    <t>FX27901</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>[정규용] 25HA8 25HA9</t>
+  </si>
+  <si>
+    <t>BG05BP</t>
+  </si>
+  <si>
+    <t>CA04K15</t>
+  </si>
+  <si>
+    <t>48L</t>
+  </si>
+  <si>
+    <t>GU29016</t>
+  </si>
+  <si>
+    <t>GW22189</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>HPW</t>
+  </si>
+  <si>
+    <t>25HA8</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>김노연</t>
+  </si>
+  <si>
+    <t>1031024</t>
+  </si>
+  <si>
+    <t>215/65R17V</t>
+  </si>
+  <si>
+    <t>T06</t>
+  </si>
+  <si>
+    <t>06/19 금</t>
+  </si>
+  <si>
+    <t>RE/DS H135</t>
+  </si>
+  <si>
+    <t>DR71842</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>DN67262</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>698</t>
+  </si>
+  <si>
+    <t>2075.0</t>
+  </si>
+  <si>
+    <t>FY24767</t>
+  </si>
+  <si>
+    <t>FX22853</t>
+  </si>
+  <si>
+    <t>730</t>
+  </si>
+  <si>
+    <t>FH23554</t>
+  </si>
+  <si>
+    <t>FX26109</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>[정규용] 22357 22358</t>
+  </si>
+  <si>
+    <t>BE46AI</t>
+  </si>
+  <si>
+    <t>CE09Z11</t>
+  </si>
+  <si>
+    <t>GU28955</t>
+  </si>
+  <si>
+    <t>GW21957</t>
+  </si>
+  <si>
+    <t>AT230</t>
+  </si>
+  <si>
+    <t>1383</t>
   </si>
   <si>
     <t>대광</t>
   </si>
   <si>
-    <t>정규용</t>
-  </si>
-  <si>
-    <t>대전공장</t>
+    <t>22357</t>
+  </si>
+  <si>
+    <t>2025-09-10</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>JF0
+Aramid JLB</t>
+  </si>
+  <si>
+    <t>DR75496</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>598</t>
+  </si>
+  <si>
+    <t>2195.0</t>
+  </si>
+  <si>
+    <t>FY24869</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>FS00819</t>
+  </si>
+  <si>
+    <t>ET10203</t>
+  </si>
+  <si>
+    <t>FHB0024</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>FX27897</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>ET10151</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>BJ01BP</t>
+  </si>
+  <si>
+    <t>CE01X12</t>
+  </si>
+  <si>
+    <t>GU29392</t>
+  </si>
+  <si>
+    <t>GW46409</t>
+  </si>
+  <si>
+    <t>AT220</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>김도형</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>06/15 월</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>RE/DS H133</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>에스텍</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>[정규용] 25GZ2 25GZ3</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>B/W</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>DN69009</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>B1007</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>장아영</t>
+  </si>
+  <si>
+    <t>2026052333</t>
+  </si>
+  <si>
+    <t>1039715</t>
+  </si>
+  <si>
+    <t>235/55R19V XL</t>
+  </si>
+  <si>
+    <t>H755A</t>
+  </si>
+  <si>
+    <t>S00</t>
+  </si>
+  <si>
+    <t>06/18 목</t>
+  </si>
+  <si>
+    <t>RE/DS H185</t>
+  </si>
+  <si>
+    <t>Transfer Dev.</t>
+  </si>
+  <si>
+    <t>P61</t>
+  </si>
+  <si>
+    <t>DR75342</t>
+  </si>
+  <si>
+    <t>DN70037</t>
+  </si>
+  <si>
+    <t>FY24792</t>
+  </si>
+  <si>
+    <t>FX22860</t>
+  </si>
+  <si>
+    <t>FD23138</t>
+  </si>
+  <si>
+    <t>FH23375</t>
+  </si>
+  <si>
+    <t>FX27873</t>
+  </si>
+  <si>
+    <t>CE09L12</t>
+  </si>
+  <si>
+    <t>GU28445</t>
+  </si>
+  <si>
+    <t>GW21965</t>
+  </si>
+  <si>
+    <t>AT235+</t>
+  </si>
+  <si>
+    <t>이장한</t>
+  </si>
+  <si>
+    <t>2026052257</t>
+  </si>
+  <si>
+    <t>1039714</t>
+  </si>
+  <si>
+    <t>235/60R18V XL</t>
+  </si>
+  <si>
+    <t>RE/DS H172</t>
+  </si>
+  <si>
+    <t>DR75520</t>
+  </si>
+  <si>
+    <t>DN70053</t>
+  </si>
+  <si>
+    <t>FY24874</t>
+  </si>
+  <si>
+    <t>FX30397</t>
+  </si>
+  <si>
+    <t>ET10416</t>
+  </si>
+  <si>
+    <t>FX27726</t>
+  </si>
+  <si>
+    <t>FH22815</t>
+  </si>
+  <si>
+    <t>FX27874</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>BE44AI</t>
+  </si>
+  <si>
+    <t>GU27006</t>
+  </si>
+  <si>
+    <t>GW21932</t>
+  </si>
+  <si>
+    <t>AH245+</t>
+  </si>
+  <si>
+    <t>B1003</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>[정규용] 26636 26637</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>선행 검증 (정규 규격)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>[정규용] 26638 26639</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>2026-01-27</t>
+  </si>
+  <si>
+    <t>신우</t>
+  </si>
+  <si>
+    <t>19E15</t>
   </si>
   <si>
     <t>이준탁</t>
   </si>
   <si>
+    <t>1462</t>
+  </si>
+  <si>
+    <t>GW21956</t>
+  </si>
+  <si>
+    <t>GU28436</t>
+  </si>
+  <si>
+    <t>BE43AI</t>
+  </si>
+  <si>
+    <t>[정규용] 19E15 19E16</t>
+  </si>
+  <si>
+    <t>P2000D/2</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>ES20425</t>
+  </si>
+  <si>
+    <t>FX26552</t>
+  </si>
+  <si>
+    <t>FHB0040</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>ET10135</t>
+  </si>
+  <si>
+    <t>FD24382</t>
+  </si>
+  <si>
+    <t>FY24753</t>
+  </si>
+  <si>
+    <t>1975.0</t>
+  </si>
+  <si>
+    <t>626</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>DN70006</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
     <t>B1003</t>
   </si>
   <si>
-    <t>FY24753</t>
-  </si>
-  <si>
-    <t>ET10135</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>P2000D/2</t>
-  </si>
-  <si>
-    <t>47M</t>
-  </si>
-  <si>
-    <t>입고</t>
-  </si>
-  <si>
-    <t>JF505
+    <t>DR75259</t>
+  </si>
+  <si>
+    <t>P84</t>
+  </si>
+  <si>
+    <t>RE/DS H184</t>
+  </si>
+  <si>
+    <t>T17</t>
+  </si>
+  <si>
+    <t>W330</t>
+  </si>
+  <si>
+    <t>225/50R18V XL</t>
+  </si>
+  <si>
+    <t>1026312</t>
+  </si>
+  <si>
+    <t>JF5
 P2000D/2</t>
   </si>
   <si>
-    <t>1038542</t>
-  </si>
-  <si>
-    <t>225/50R17V XL</t>
-  </si>
-  <si>
-    <t>LH43</t>
-  </si>
-  <si>
-    <t>LF</t>
-  </si>
-  <si>
-    <t>06/10 수</t>
-  </si>
-  <si>
-    <t>P61</t>
-  </si>
-  <si>
-    <t>DR75485</t>
-  </si>
-  <si>
-    <t>234</t>
-  </si>
-  <si>
-    <t>DN69749</t>
-  </si>
-  <si>
-    <t>B1007</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>654</t>
-  </si>
-  <si>
-    <t>1895.0</t>
-  </si>
-  <si>
-    <t>FY24820</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>FX31388</t>
-  </si>
-  <si>
-    <t>530</t>
-  </si>
-  <si>
-    <t>FH22815</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>FX27874</t>
-  </si>
-  <si>
-    <t>185</t>
+    <t>정기중</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>23주 규격</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>26년 24주차 양시 주간 계획 (2026-06-15~2026-06-20)_V5.0</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>SYT</t>
+  </si>
+  <si>
+    <t>25HA4</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>AT115</t>
+  </si>
+  <si>
+    <t>GW21496</t>
+  </si>
+  <si>
+    <t>GU29105</t>
+  </si>
+  <si>
+    <t>CA04K14</t>
+  </si>
+  <si>
+    <t>BG47BI</t>
+  </si>
+  <si>
+    <t>[정규용] 25HA4 25HA5</t>
   </si>
   <si>
     <t>ET11001</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>[정규용] 25FQ8 25FQ9</t>
-  </si>
-  <si>
-    <t>GU28198</t>
-  </si>
-  <si>
-    <t>GW21957</t>
-  </si>
-  <si>
-    <t>1383</t>
-  </si>
-  <si>
-    <t>SYT</t>
-  </si>
-  <si>
-    <t>25FQ8</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2025-12-03</t>
-  </si>
-  <si>
-    <t>양산기술</t>
-  </si>
-  <si>
-    <t>2022630</t>
-  </si>
-  <si>
-    <t>205/75R16C</t>
-  </si>
-  <si>
-    <t>RA58</t>
-  </si>
-  <si>
-    <t>T02</t>
-  </si>
-  <si>
-    <t>30
-(100)</t>
-  </si>
-  <si>
-    <t>06/11 목</t>
-  </si>
-  <si>
-    <t>RE/DS H181</t>
-  </si>
-  <si>
-    <t>Transfer Dev.</t>
-  </si>
-  <si>
-    <t>T95</t>
-  </si>
-  <si>
-    <t>U35
-(F)</t>
-  </si>
-  <si>
-    <t>DR75477</t>
-  </si>
-  <si>
-    <t>DN69694</t>
-  </si>
-  <si>
-    <t>B1005</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>760</t>
-  </si>
-  <si>
-    <t>2050.0</t>
-  </si>
-  <si>
-    <t>FY25519</t>
-  </si>
-  <si>
-    <t>450</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>FR02911</t>
-  </si>
-  <si>
-    <t>ET10203</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>FW01566</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>FHB0152</t>
-  </si>
-  <si>
-    <t>ES20427</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>FH23974</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>DN56899</t>
-  </si>
-  <si>
-    <t>CQB86</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>[정규용] 24Q26 24Q27</t>
-  </si>
-  <si>
-    <t>B52750</t>
-  </si>
-  <si>
-    <t>CA02L17</t>
-  </si>
-  <si>
-    <t>GU28569</t>
-  </si>
-  <si>
-    <t>GW66006</t>
-  </si>
-  <si>
-    <t>BB315</t>
-  </si>
-  <si>
-    <t>1289</t>
-  </si>
-  <si>
-    <t>24Q26</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>이한빛</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>장시봉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>담당 : 이운규 010-6455-0564 (72-1555)</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>BE38AI</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026052545</t>
+    <t>FX27689</t>
+  </si>
+  <si>
+    <t>FHB0103</t>
+  </si>
+  <si>
+    <t>FX26705</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>FY24865</t>
+  </si>
+  <si>
+    <t>2015.0</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>DN69802</t>
+  </si>
+  <si>
+    <t>B1004</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>DR75351</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>RE/DS H132</t>
+  </si>
+  <si>
+    <t>IK41</t>
+  </si>
+  <si>
+    <t>235/40R20V XL</t>
+  </si>
+  <si>
+    <t>1038794</t>
   </si>
   <si>
     <t>JF505</t>
-  </si>
-  <si>
-    <t>1039713</t>
-  </si>
-  <si>
-    <t>215/55R17V</t>
-  </si>
-  <si>
-    <t>H755</t>
-  </si>
-  <si>
-    <t>S00</t>
-  </si>
-  <si>
-    <t>RE/DS H152</t>
-  </si>
-  <si>
-    <t>DR75519</t>
-  </si>
-  <si>
-    <t>DN70052</t>
-  </si>
-  <si>
-    <t>FD24387</t>
-  </si>
-  <si>
-    <t>ET10416</t>
-  </si>
-  <si>
-    <t>FH23551</t>
-  </si>
-  <si>
-    <t>ES20424</t>
-  </si>
-  <si>
-    <t>FX26277</t>
-  </si>
-  <si>
-    <t>[정규용] 26634 26635</t>
-  </si>
-  <si>
-    <t>BE38AI</t>
-  </si>
-  <si>
-    <t>CE09L10</t>
-  </si>
-  <si>
-    <t>AT225+</t>
-  </si>
-  <si>
-    <t>* 선행 검증 규격</t>
-  </si>
-  <si>
-    <t>HPW</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>이장한</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>RE/DS H152</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>06/12 금</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>26년 23주차 양시 주간 계획 (2026-06-08~2026-06-13)_V4.0</t>
-    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -856,6 +1287,22 @@
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF00A000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00A000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color rgb="FF0000FF"/>
       <name val="맑은 고딕"/>
@@ -873,6 +1320,14 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color rgb="FFFF6600"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF008000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -881,7 +1336,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FFFF33CC"/>
+      <color rgb="FF0033CC"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -896,13 +1351,21 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0033CC"/>
+      <color rgb="FF7030A0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF33CC"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -935,18 +1398,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE4DFEC"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -969,11 +1438,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -994,7 +1476,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1027,55 +1509,109 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1086,8 +1622,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFE4DFEC"/>
       <color rgb="FF0000FF"/>
+      <color rgb="FFEBF1DE"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1386,7 +1922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CL5"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" outlineLevelCol="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1423,8 +1959,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:89" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
-        <v>231</v>
+      <c r="A1" s="38" t="s">
+        <v>344</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1499,7 +2035,7 @@
       <c r="BT1" s="1"/>
       <c r="BU1" s="1"/>
       <c r="BV1" s="1" t="s">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
@@ -1519,40 +2055,40 @@
     </row>
     <row r="2" spans="1:89" ht="64.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>11</v>
+        <v>263</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>12</v>
@@ -1786,783 +2322,2313 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:89" ht="64.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
         <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>90</v>
+        <v>313</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>91</v>
       </c>
       <c r="E3" s="7">
-        <v>2026052206</v>
+        <v>2026051235</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>124</v>
+        <v>341</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>125</v>
+        <v>340</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>126</v>
+        <v>339</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>127</v>
+        <v>338</v>
       </c>
       <c r="J3" s="12">
         <v>4</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>97</v>
+        <v>337</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q3" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="R3" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="S3" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="R3" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="S3" s="15" t="s">
-        <v>99</v>
-      </c>
       <c r="T3" s="16" t="s">
-        <v>130</v>
+        <v>335</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="X3" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>103</v>
+        <v>334</v>
+      </c>
+      <c r="Y3" s="13" t="s">
+        <v>333</v>
       </c>
       <c r="Z3" s="16" t="s">
-        <v>132</v>
+        <v>332</v>
       </c>
       <c r="AA3" s="16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AB3" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC3" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="AD3" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="AC3" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="AD3" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="AE3" s="13" t="s">
-        <v>135</v>
+        <v>330</v>
       </c>
       <c r="AF3" s="13" t="s">
-        <v>136</v>
+        <v>329</v>
       </c>
       <c r="AG3" s="13" t="s">
-        <v>137</v>
+        <v>328</v>
       </c>
       <c r="AH3" s="13" t="s">
-        <v>138</v>
+        <v>327</v>
       </c>
       <c r="AI3" s="13" t="s">
-        <v>139</v>
+        <v>242</v>
       </c>
       <c r="AJ3" s="13" t="s">
-        <v>140</v>
+        <v>243</v>
       </c>
       <c r="AK3" s="13" t="s">
-        <v>141</v>
+        <v>326</v>
       </c>
       <c r="AL3" s="19" t="s">
-        <v>119</v>
+        <v>325</v>
       </c>
       <c r="AM3" s="13" t="s">
-        <v>142</v>
+        <v>324</v>
       </c>
       <c r="AN3" s="13" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="AO3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AP3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AQ3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AR3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AS3" s="13" t="s">
-        <v>143</v>
+        <v>323</v>
       </c>
       <c r="AT3" s="13" t="s">
-        <v>107</v>
+        <v>321</v>
       </c>
       <c r="AU3" s="13" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="AV3" s="13" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="AW3" s="13" t="s">
-        <v>145</v>
+        <v>322</v>
       </c>
       <c r="AX3" s="13" t="s">
-        <v>107</v>
+        <v>321</v>
       </c>
       <c r="AY3" s="13" t="s">
-        <v>146</v>
+        <v>320</v>
       </c>
       <c r="AZ3" s="13" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="BA3" s="13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="BB3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="BC3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="BD3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="BE3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="BG3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="BH3" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BI3" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="BJ3" s="13" t="s">
-        <v>121</v>
+        <v>319</v>
       </c>
       <c r="BK3" s="13"/>
       <c r="BL3" s="13" t="s">
-        <v>148</v>
+        <v>300</v>
       </c>
       <c r="BM3" s="13" t="s">
-        <v>149</v>
+        <v>318</v>
       </c>
       <c r="BN3" s="13" t="s">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="BO3" s="16" t="s">
-        <v>95</v>
+        <v>226</v>
       </c>
       <c r="BP3" s="16" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BQ3" s="15"/>
       <c r="BR3" s="17" t="s">
-        <v>150</v>
+        <v>316</v>
       </c>
       <c r="BS3" s="17" t="s">
-        <v>151</v>
+        <v>315</v>
       </c>
       <c r="BT3" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="BU3" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="BV3" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="BW3" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="BU3" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="BV3" s="18"/>
-      <c r="BW3" s="15" t="s">
-        <v>112</v>
-      </c>
       <c r="BX3" s="19" t="s">
-        <v>153</v>
+        <v>311</v>
       </c>
       <c r="BY3" s="15" t="s">
-        <v>95</v>
+        <v>206</v>
       </c>
       <c r="BZ3" s="15" t="s">
-        <v>90</v>
+        <v>313</v>
       </c>
       <c r="CA3" s="15" t="s">
-        <v>154</v>
+        <v>312</v>
       </c>
       <c r="CB3" s="15" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="CC3" s="15" t="s">
         <v>114</v>
       </c>
       <c r="CD3" s="15" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="CE3" s="15" t="s">
-        <v>153</v>
+        <v>311</v>
       </c>
       <c r="CF3" s="15" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="CG3" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="CH3" s="15"/>
+        <v>234</v>
+      </c>
+      <c r="CH3" s="15" t="s">
+        <v>309</v>
+      </c>
       <c r="CI3" s="15"/>
       <c r="CJ3" s="15"/>
       <c r="CK3" s="15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>91</v>
       </c>
       <c r="E4" s="7">
-        <v>2026051907</v>
+        <v>2026052724</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>159</v>
+        <v>94</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="J4" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q4" s="21" t="s">
-        <v>163</v>
+        <v>100</v>
+      </c>
+      <c r="Q4" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="V4" s="16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="X4" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y4" s="13" t="s">
-        <v>117</v>
+        <v>236</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>105</v>
       </c>
       <c r="Z4" s="16" t="s">
-        <v>120</v>
+        <v>237</v>
       </c>
       <c r="AA4" s="16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AB4" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC4" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD4" s="13" t="s">
-        <v>170</v>
+        <v>107</v>
+      </c>
+      <c r="AC4" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD4" s="35" t="s">
+        <v>265</v>
       </c>
       <c r="AE4" s="13" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="AF4" s="13" t="s">
-        <v>172</v>
+        <v>239</v>
       </c>
       <c r="AG4" s="13" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="AH4" s="13" t="s">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="AI4" s="13" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="AJ4" s="13" t="s">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="AK4" s="13" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="AL4" s="13" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="AM4" s="13" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="AN4" s="13" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="AO4" s="13" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="AP4" s="13" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="AQ4" s="13" t="s">
-        <v>181</v>
+        <v>92</v>
       </c>
       <c r="AR4" s="13" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AS4" s="13" t="s">
-        <v>182</v>
+        <v>246</v>
       </c>
       <c r="AT4" s="13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AU4" s="13" t="s">
-        <v>184</v>
+        <v>247</v>
       </c>
       <c r="AV4" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW4" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="AX4" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="AY4" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="AZ4" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BA4" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="BB4" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="BC4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH4" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="BI4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ4" s="13" t="s">
         <v>108</v>
-      </c>
-      <c r="AW4" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="AX4" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AY4" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="AZ4" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BA4" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="BB4" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="BC4" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="BD4" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="BE4" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF4" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="BG4" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="BH4" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="BI4" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="BJ4" s="13" t="s">
-        <v>110</v>
       </c>
       <c r="BK4" s="13"/>
       <c r="BL4" s="13" t="s">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="BM4" s="13" t="s">
-        <v>191</v>
+        <v>262</v>
       </c>
       <c r="BN4" s="13" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="BO4" s="16" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="BP4" s="16" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BQ4" s="15"/>
       <c r="BR4" s="17" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="BS4" s="17" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="BT4" s="17" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="BU4" s="17" t="s">
-        <v>197</v>
+        <v>257</v>
       </c>
       <c r="BV4" s="18"/>
       <c r="BW4" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BX4" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="BY4" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="BZ4" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="CA4" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="BY4" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="BZ4" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA4" s="15" t="s">
-        <v>198</v>
-      </c>
       <c r="CB4" s="15" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="CC4" s="15" t="s">
         <v>114</v>
       </c>
       <c r="CD4" s="15" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="CE4" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="CF4" s="15" t="s">
-        <v>199</v>
+        <v>116</v>
       </c>
       <c r="CG4" s="15" t="s">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="CH4" s="15" t="s">
-        <v>201</v>
+        <v>118</v>
       </c>
       <c r="CI4" s="15"/>
       <c r="CJ4" s="15"/>
       <c r="CK4" s="15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="23" t="s">
+      <c r="B5" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="7">
+        <v>2026060518</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="J5" s="12">
+        <v>4</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="S5" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="T5" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="U5" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="V5" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="W5" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="Z5" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA5" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB5" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC5" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="AD5" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE5" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="AF5" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="AG5" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="AH5" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="AI5" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="AJ5" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="AK5" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="AL5" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="AM5" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="AN5" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AO5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS5" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="AT5" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AU5" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="AV5" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW5" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="AX5" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY5" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="AZ5" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BA5" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="BB5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH5" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="BI5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ5" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK5" s="13"/>
+      <c r="BL5" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="BM5" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="BN5" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="BO5" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="BP5" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ5" s="15"/>
+      <c r="BR5" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="BS5" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="BT5" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="BU5" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="BV5" s="18"/>
+      <c r="BW5" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="BX5" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="BY5" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="BZ5" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="F5" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="H5" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="I5" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="J5" s="27">
-        <v>4</v>
-      </c>
-      <c r="K5" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="L5" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="M5" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="N5" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="O5" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="P5" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q5" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="R5" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="S5" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="T5" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="U5" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="V5" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="W5" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="X5" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="Y5" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z5" s="30">
-        <v>232</v>
-      </c>
-      <c r="AA5" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB5" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC5" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="AD5" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE5" s="28">
-        <v>135</v>
-      </c>
-      <c r="AF5" s="28">
-        <v>628</v>
-      </c>
-      <c r="AG5" s="28">
-        <v>1935</v>
-      </c>
-      <c r="AH5" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI5" s="28">
-        <v>410</v>
-      </c>
-      <c r="AJ5" s="28">
-        <v>375</v>
-      </c>
-      <c r="AK5" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="AL5" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="AM5" s="28">
-        <v>520</v>
-      </c>
-      <c r="AN5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="AO5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="AQ5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="AS5" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="AT5" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="AU5" s="28">
-        <v>190</v>
-      </c>
-      <c r="AV5" s="28">
-        <v>27</v>
-      </c>
-      <c r="AW5" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="AX5" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="AY5" s="28">
-        <v>180</v>
-      </c>
-      <c r="AZ5" s="28">
-        <v>27</v>
-      </c>
-      <c r="BA5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="BB5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="BC5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="BD5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="BE5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="BG5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="BH5" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="BI5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="BJ5" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="BK5" s="28"/>
-      <c r="BL5" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="BM5" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="BN5" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="BO5" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="BP5" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="BQ5" s="29"/>
-      <c r="BR5" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="BS5" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="BT5" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="BU5" s="31">
-        <v>1383</v>
-      </c>
-      <c r="BV5" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="BW5" s="29"/>
-      <c r="BX5" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="BY5" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="BZ5" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="CA5" s="15">
-        <v>26634</v>
+      <c r="CA5" s="15" t="s">
+        <v>347</v>
       </c>
       <c r="CB5" s="15" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="CC5" s="15" t="s">
         <v>114</v>
       </c>
       <c r="CD5" s="15" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="CE5" s="15" t="s">
-        <v>225</v>
+        <v>346</v>
       </c>
       <c r="CF5" s="15" t="s">
-        <v>226</v>
+        <v>345</v>
       </c>
       <c r="CG5" s="15" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="CH5" s="15"/>
       <c r="CI5" s="15"/>
       <c r="CJ5" s="15"/>
       <c r="CK5" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2026052537</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="J6" s="12">
+        <v>4</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="S6" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="T6" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="U6" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="V6" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="W6" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="X6" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y6" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z6" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA6" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB6" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC6" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD6" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE6" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF6" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="AG6" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="AH6" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="AI6" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ6" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="AK6" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="AL6" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM6" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="AN6" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AO6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS6" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="AT6" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AU6" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV6" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW6" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="AX6" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY6" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="AZ6" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BA6" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="BB6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH6" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="BI6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ6" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK6" s="13"/>
+      <c r="BL6" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="BM6" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="BN6" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="BO6" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="BP6" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ6" s="15"/>
+      <c r="BR6" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="BS6" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="BT6" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="BU6" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="BV6" s="18"/>
+      <c r="BW6" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="BX6" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="BY6" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="BZ6" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="CA6" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="CB6" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="CC6" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="CD6" s="15" t="s">
         <v>115</v>
+      </c>
+      <c r="CE6" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="CF6" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="CG6" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="CH6" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="CI6" s="15"/>
+      <c r="CJ6" s="15"/>
+      <c r="CK6" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="H7" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="J7" s="43">
+        <v>4</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="M7" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="O7" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="P7" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="R7" s="47" t="s">
+        <v>273</v>
+      </c>
+      <c r="S7" s="48" t="s">
+        <v>274</v>
+      </c>
+      <c r="T7" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="U7" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="V7" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="W7" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="X7" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y7" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="Z7" s="49">
+        <v>240</v>
+      </c>
+      <c r="AA7" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB7" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC7" s="44" t="s">
+        <v>277</v>
+      </c>
+      <c r="AD7" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE7" s="44">
+        <v>150</v>
+      </c>
+      <c r="AF7" s="44">
+        <v>704</v>
+      </c>
+      <c r="AG7" s="44">
+        <v>2165</v>
+      </c>
+      <c r="AH7" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="AI7" s="44">
+        <v>450</v>
+      </c>
+      <c r="AJ7" s="44">
+        <v>415</v>
+      </c>
+      <c r="AK7" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="AL7" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM7" s="44">
+        <v>580</v>
+      </c>
+      <c r="AN7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO7" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="AP7" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="AQ7" s="44">
+        <v>480</v>
+      </c>
+      <c r="AR7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS7" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="AT7" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="AU7" s="44">
+        <v>205</v>
+      </c>
+      <c r="AV7" s="44">
+        <v>27</v>
+      </c>
+      <c r="AW7" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="AX7" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="AY7" s="44">
+        <v>195</v>
+      </c>
+      <c r="AZ7" s="44">
+        <v>27</v>
+      </c>
+      <c r="BA7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BB7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH7" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ7" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK7" s="44"/>
+      <c r="BL7" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="BM7" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="BN7" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="BO7" s="49" t="s">
+        <v>283</v>
+      </c>
+      <c r="BP7" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ7" s="48"/>
+      <c r="BR7" s="50" t="s">
+        <v>284</v>
+      </c>
+      <c r="BS7" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="BT7" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="BU7" s="50">
+        <v>1546</v>
+      </c>
+      <c r="BV7" s="51" t="s">
+        <v>307</v>
+      </c>
+      <c r="BW7" s="48"/>
+      <c r="BX7" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="BY7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="BZ7" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="CA7" s="15"/>
+      <c r="CB7" s="15"/>
+      <c r="CC7" s="15"/>
+      <c r="CD7" s="15"/>
+      <c r="CE7" s="15"/>
+      <c r="CF7" s="15"/>
+      <c r="CG7" s="15"/>
+      <c r="CH7" s="15"/>
+      <c r="CI7" s="15"/>
+      <c r="CJ7" s="15"/>
+      <c r="CK7" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2026051663</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="J8" s="12">
+        <v>4</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="T8" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="U8" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="V8" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="W8" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="X8" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y8" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z8" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA8" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB8" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC8" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD8" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE8" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF8" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AG8" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="AH8" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI8" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="AJ8" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="AK8" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="AL8" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM8" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="AN8" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AO8" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="AP8" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="AQ8" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="AR8" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AS8" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="AT8" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="AU8" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="AV8" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW8" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="AX8" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="AY8" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="AZ8" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BA8" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="BB8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ8" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK8" s="13"/>
+      <c r="BL8" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="BM8" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="BN8" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="BO8" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="BP8" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="BQ8" s="15"/>
+      <c r="BR8" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="BS8" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="BT8" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="BU8" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="BV8" s="18"/>
+      <c r="BW8" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="BX8" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="BY8" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="BZ8" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="CA8" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="CB8" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="CC8" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="CD8" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="CE8" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="CF8" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="CG8" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="CH8" s="15"/>
+      <c r="CI8" s="15"/>
+      <c r="CJ8" s="15"/>
+      <c r="CK8" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>288</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="H9" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="J9" s="43">
+        <v>4</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="N9" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="O9" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="P9" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="R9" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="S9" s="48" t="s">
+        <v>274</v>
+      </c>
+      <c r="T9" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="U9" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="V9" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="W9" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="X9" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y9" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z9" s="49">
+        <v>248</v>
+      </c>
+      <c r="AA9" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB9" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC9" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="AD9" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE9" s="44">
+        <v>170</v>
+      </c>
+      <c r="AF9" s="44">
+        <v>764</v>
+      </c>
+      <c r="AG9" s="44">
+        <v>2160</v>
+      </c>
+      <c r="AH9" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="AI9" s="44">
+        <v>470</v>
+      </c>
+      <c r="AJ9" s="44">
+        <v>435</v>
+      </c>
+      <c r="AK9" s="44" t="s">
+        <v>295</v>
+      </c>
+      <c r="AL9" s="44" t="s">
+        <v>296</v>
+      </c>
+      <c r="AM9" s="44">
+        <v>610</v>
+      </c>
+      <c r="AN9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO9" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="AP9" s="44" t="s">
+        <v>296</v>
+      </c>
+      <c r="AQ9" s="44">
+        <v>490</v>
+      </c>
+      <c r="AR9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS9" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="AT9" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="AU9" s="44">
+        <v>195</v>
+      </c>
+      <c r="AV9" s="44">
+        <v>27</v>
+      </c>
+      <c r="AW9" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="AX9" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="AY9" s="44">
+        <v>185</v>
+      </c>
+      <c r="AZ9" s="44">
+        <v>27</v>
+      </c>
+      <c r="BA9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BB9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH9" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="BI9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ9" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK9" s="44"/>
+      <c r="BL9" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="BM9" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="BN9" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="BO9" s="49" t="s">
+        <v>226</v>
+      </c>
+      <c r="BP9" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ9" s="48"/>
+      <c r="BR9" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="BS9" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="BT9" s="50" t="s">
+        <v>304</v>
+      </c>
+      <c r="BU9" s="50">
+        <v>1466</v>
+      </c>
+      <c r="BV9" s="51" t="s">
+        <v>307</v>
+      </c>
+      <c r="BW9" s="48"/>
+      <c r="BX9" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="BY9" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="BZ9" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="CA9" s="15"/>
+      <c r="CB9" s="15"/>
+      <c r="CC9" s="15"/>
+      <c r="CD9" s="15"/>
+      <c r="CE9" s="15"/>
+      <c r="CF9" s="15"/>
+      <c r="CG9" s="15"/>
+      <c r="CH9" s="15"/>
+      <c r="CI9" s="15"/>
+      <c r="CJ9" s="15"/>
+      <c r="CK9" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="20">
+        <v>2026052387</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="J10" s="25">
+        <v>4</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="N10" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="O10" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="P10" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="R10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="S10" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="T10" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="U10" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="V10" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="W10" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="X10" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y10" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z10" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA10" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB10" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC10" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD10" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE10" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF10" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG10" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH10" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI10" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ10" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="AK10" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL10" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM10" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="AN10" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="AO10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS10" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="AT10" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="AU10" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV10" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW10" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="AX10" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY10" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="AZ10" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="BA10" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="BB10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH10" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="BI10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ10" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK10" s="26"/>
+      <c r="BL10" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="BM10" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN10" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="BO10" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP10" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ10" s="28"/>
+      <c r="BR10" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="BS10" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="BT10" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="BU10" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="BV10" s="31"/>
+      <c r="BW10" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="BX10" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="BY10" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="BZ10" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="CA10" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="CB10" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CC10" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="CD10" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="CE10" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="CF10" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="CG10" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="CH10" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="CI10" s="28"/>
+      <c r="CJ10" s="28"/>
+      <c r="CK10" s="28" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1181102362204724" right="0.1181102362204724" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="27" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c8840f99-d2c0-44c8-b3c0-1cf7ba624ece" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100B097CCE3169ADA4BA25858E524454EC4" ma:contentTypeVersion="14" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="3e6975e3a721e0d03eb2371d6d886909">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c8840f99-d2c0-44c8-b3c0-1cf7ba624ece" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5d21d68b88ca7e122f7a0413de0384d" ns3:_="">
+    <xsd:import namespace="c8840f99-d2c0-44c8-b3c0-1cf7ba624ece"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c8840f99-d2c0-44c8-b3c0-1cf7ba624ece" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="17" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="18" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="콘텐츠 형식"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="제목"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BD26E16-0988-4DE3-91E0-047F3AEBE336}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c8840f99-d2c0-44c8-b3c0-1cf7ba624ece"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44BB576B-BEF0-44B6-847E-39BCC4E6BCBD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C2DC145-33C8-4352-A905-4655EA1FB3A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c8840f99-d2c0-44c8-b3c0-1cf7ba624ece"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>